--- a/Models/Яйца/results/Яйца - Результаты прогнозов SARIMA.xlsx
+++ b/Models/Яйца/results/Яйца - Результаты прогнозов SARIMA.xlsx
@@ -488,41 +488,41 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(1, 0, 2)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>(2, 1, 1, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5051.7</v>
+        <v>1659.5</v>
       </c>
       <c r="G2" t="n">
-        <v>4697.7</v>
+        <v>1446.79</v>
       </c>
       <c r="H2" t="n">
-        <v>8.609999999999999</v>
+        <v>2.42</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>[51074.36, 50913.26, 57034.71]</t>
+          <t>[60496.69, 57883.82, 57592.39]</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>[46739.2, 48287.8, 64167.2]</t>
+          <t>[62899.9, 58300.1, 56071.5]</t>
         </is>
       </c>
     </row>
@@ -534,41 +534,41 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(3, 0, 0)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>7628.01</v>
+        <v>2189.52</v>
       </c>
       <c r="G3" t="n">
-        <v>6410.64</v>
+        <v>1972.91</v>
       </c>
       <c r="H3" t="n">
-        <v>10.45</v>
+        <v>3.62</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>[47185.39, 52980.57, 52720.73]</t>
+          <t>[58930.54, 58742.61, 54830.89]</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>[48287.8, 64167.2, 59663.6]</t>
+          <t>[58300.1, 56071.5, 52213.7]</t>
         </is>
       </c>
     </row>
@@ -580,41 +580,41 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>(1, 0, 5)</t>
+          <t>(3, 0, 0)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>(2, 1, 1, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>7107.01</v>
+        <v>2772.33</v>
       </c>
       <c r="G4" t="n">
-        <v>5837.03</v>
+        <v>2717.35</v>
       </c>
       <c r="H4" t="n">
-        <v>9.35</v>
+        <v>4.96</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>[53302.02, 53953.95, 59775.33]</t>
+          <t>[58407.02, 54536.02, 59134.52]</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>[64167.2, 59663.6, 60711.6]</t>
+          <t>[56071.5, 52213.7, 55640.3]</t>
         </is>
       </c>
     </row>
@@ -626,17 +626,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>(1, 0, 3)</t>
+          <t>(3, 0, 0)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -645,22 +645,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>5608.71</v>
+        <v>1684.89</v>
       </c>
       <c r="G5" t="n">
-        <v>4964.34</v>
+        <v>1500.86</v>
       </c>
       <c r="H5" t="n">
-        <v>8.19</v>
+        <v>2.76</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>[57769.02, 65435.48, 69042.15]</t>
+          <t>[53445.23, 58184.12, 53601.77]</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>[59663.6, 60711.6, 60767.6]</t>
+          <t>[52213.7, 55640.3, 54329.0]</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>(1, 0, 3)</t>
+          <t>(1, 0, 2)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -691,22 +691,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>6951.16</v>
+        <v>4124.61</v>
       </c>
       <c r="G6" t="n">
-        <v>6687.66</v>
+        <v>3276.39</v>
       </c>
       <c r="H6" t="n">
-        <v>10.86</v>
+        <v>6.86</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>[66599.09, 70071.33, 69142.06]</t>
+          <t>[57321.36, 52994.98, 51945.68]</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>[60711.6, 60767.6, 64270.3]</t>
+          <t>[55640.3, 54329.0, 45131.6]</t>
         </is>
       </c>
     </row>
@@ -718,17 +718,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>(1, 0, 3)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -737,22 +737,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3638.56</v>
+        <v>3865.71</v>
       </c>
       <c r="G7" t="n">
-        <v>2835.77</v>
+        <v>3371.81</v>
       </c>
       <c r="H7" t="n">
-        <v>4.6</v>
+        <v>6.85</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>[66730.14, 66223.72, 62308.56]</t>
+          <t>[52090.27, 51167.34, 58543.86]</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>[60767.6, 64270.3, 62899.9]</t>
+          <t>[54329.0, 45131.6, 60384.8]</t>
         </is>
       </c>
     </row>
@@ -764,17 +764,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>(3, 0, 0)</t>
+          <t>(2, 0, 2)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2731.7</v>
+        <v>5220.2</v>
       </c>
       <c r="G8" t="n">
-        <v>2586.12</v>
+        <v>4235.67</v>
       </c>
       <c r="H8" t="n">
-        <v>4.16</v>
+        <v>8.76</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>[62025.42, 59106.86, 56579.66]</t>
+          <t>[52222.5, 60391.06, 58671.36]</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>[64270.3, 62899.9, 58300.1]</t>
+          <t>[45131.6, 60384.8, 53061.5]</t>
         </is>
       </c>
     </row>
@@ -810,17 +810,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>(1, 0, 2)</t>
+          <t>(3, 0, 2)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -829,22 +829,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1659.5</v>
+        <v>4020</v>
       </c>
       <c r="G9" t="n">
-        <v>1446.79</v>
+        <v>3522.98</v>
       </c>
       <c r="H9" t="n">
-        <v>2.42</v>
+        <v>5.9</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>[60496.69, 57883.82, 57592.39]</t>
+          <t>[54237.15, 54596.19, 59353.21]</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>[62899.9, 58300.1, 56071.5]</t>
+          <t>[60384.8, 53061.5, 62239.8]</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>(3, 0, 0)</t>
+          <t>(1, 0, 4)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -875,22 +875,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2189.52</v>
+        <v>2915.22</v>
       </c>
       <c r="G10" t="n">
-        <v>1972.91</v>
+        <v>2503.09</v>
       </c>
       <c r="H10" t="n">
-        <v>3.62</v>
+        <v>4.45</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>[58930.54, 58742.61, 54830.89]</t>
+          <t>[57658.29, 63447.37, 63511.32]</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>[58300.1, 56071.5, 52213.7]</t>
+          <t>[53061.5, 62239.8, 61806.4]</t>
         </is>
       </c>
     </row>
@@ -902,17 +902,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>(3, 0, 0)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -921,22 +921,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2772.33</v>
+        <v>1012.14</v>
       </c>
       <c r="G11" t="n">
-        <v>2717.35</v>
+        <v>693.53</v>
       </c>
       <c r="H11" t="n">
-        <v>4.96</v>
+        <v>1.11</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>[58407.02, 54536.02, 59134.52]</t>
+          <t>[60513.71, 61859.02, 61912.94]</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>[56071.5, 52213.7, 55640.3]</t>
+          <t>[62239.8, 61806.4, 62214.8]</t>
         </is>
       </c>
     </row>
@@ -948,12 +948,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -967,22 +967,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>625.63</v>
+        <v>1041.75</v>
       </c>
       <c r="G12" t="n">
-        <v>531.14</v>
+        <v>908.4</v>
       </c>
       <c r="H12" t="n">
-        <v>3.21</v>
+        <v>4.95</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>[16872.22, 13925.37, 16100.21]</t>
+          <t>[16248.67, 19379.05, 18029.28]</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>[17851.6, 14347.6, 15908.4]</t>
+          <t>[17751.9, 19636.9, 18993.4]</t>
         </is>
       </c>
     </row>
@@ -994,12 +994,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1013,22 +1013,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>682.35</v>
+        <v>1246.75</v>
       </c>
       <c r="G13" t="n">
-        <v>515.01</v>
+        <v>1097.95</v>
       </c>
       <c r="H13" t="n">
-        <v>3.35</v>
+        <v>5.72</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>[14380.3, 16309.48, 16309.75]</t>
+          <t>[20414.15, 18403.08, 17135.81]</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>[14347.6, 15908.4, 15198.5]</t>
+          <t>[19636.9, 18993.4, 19062.1]</t>
         </is>
       </c>
     </row>
@@ -1040,12 +1040,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1059,22 +1059,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>702.51</v>
+        <v>2025.05</v>
       </c>
       <c r="G14" t="n">
-        <v>609.23</v>
+        <v>1909.55</v>
       </c>
       <c r="H14" t="n">
-        <v>3.9</v>
+        <v>10.09</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>[16287.64, 16302.02, 17240.94]</t>
+          <t>[17985.03, 16971.34, 16145.98]</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>[15908.4, 15198.5, 16896.0]</t>
+          <t>[18993.4, 19062.1, 18775.5]</t>
         </is>
       </c>
     </row>
@@ -1086,12 +1086,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1105,22 +1105,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1282.52</v>
+        <v>1922.2</v>
       </c>
       <c r="G15" t="n">
-        <v>1055.87</v>
+        <v>1883.85</v>
       </c>
       <c r="H15" t="n">
-        <v>5.89</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>[16083.12, 17158.28, 17610.1]</t>
+          <t>[17517.58, 16357.89, 18459.19]</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>[15198.5, 16896.0, 19630.8]</t>
+          <t>[19062.1, 18775.5, 20148.6]</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1151,22 +1151,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1796.33</v>
+        <v>1522.85</v>
       </c>
       <c r="G16" t="n">
-        <v>1557</v>
+        <v>1516.12</v>
       </c>
       <c r="H16" t="n">
-        <v>7.9</v>
+        <v>8.18</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>[16603.83, 17378.05, 18116.12]</t>
+          <t>[17172.0, 18834.05, 15564.79]</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>[16896.0, 19630.8, 20242.2]</t>
+          <t>[18775.5, 20148.6, 17195.1]</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1197,22 +1197,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2158.34</v>
+        <v>1274.04</v>
       </c>
       <c r="G17" t="n">
-        <v>2154.65</v>
+        <v>1120.72</v>
       </c>
       <c r="H17" t="n">
-        <v>11.29</v>
+        <v>6.06</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>[17552.7, 18188.9, 15419.35]</t>
+          <t>[19841.64, 15900.1, 17521.4]</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>[19630.8, 20242.2, 17751.9]</t>
+          <t>[20148.6, 17195.1, 19281.6]</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1243,22 +1243,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1219.61</v>
+        <v>1957.85</v>
       </c>
       <c r="G18" t="n">
-        <v>1050.96</v>
+        <v>1849.15</v>
       </c>
       <c r="H18" t="n">
-        <v>5.65</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>[19425.7, 15853.54, 19198.87]</t>
+          <t>[16044.83, 17587.42, 16768.91]</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>[20242.2, 17751.9, 19636.9]</t>
+          <t>[17195.1, 19281.6, 19471.9]</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1289,22 +1289,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1041.75</v>
+        <v>1732.64</v>
       </c>
       <c r="G19" t="n">
-        <v>908.4</v>
+        <v>1624.77</v>
       </c>
       <c r="H19" t="n">
-        <v>4.95</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>[16248.67, 19379.05, 18029.28]</t>
+          <t>[18336.36, 17063.62, 18400.7]</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>[17751.9, 19636.9, 18993.4]</t>
+          <t>[19281.6, 19471.9, 19921.5]</t>
         </is>
       </c>
     </row>
@@ -1316,17 +1316,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>(5, 1, 0)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1335,22 +1335,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1246.75</v>
+        <v>1349.02</v>
       </c>
       <c r="G20" t="n">
-        <v>1097.95</v>
+        <v>1326.65</v>
       </c>
       <c r="H20" t="n">
-        <v>5.72</v>
+        <v>6.72</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>[20414.15, 18403.08, 17135.81]</t>
+          <t>[18034.61, 18934.09, 21421.84]</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>[19636.9, 18993.4, 19062.1]</t>
+          <t>[19471.9, 19921.5, 19866.6]</t>
         </is>
       </c>
     </row>
@@ -1362,17 +1362,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>(5, 1, 0)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1381,22 +1381,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2025.05</v>
+        <v>1735.32</v>
       </c>
       <c r="G21" t="n">
-        <v>1909.55</v>
+        <v>1413.03</v>
       </c>
       <c r="H21" t="n">
-        <v>10.09</v>
+        <v>6.94</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>[17985.03, 16971.34, 16145.98]</t>
+          <t>[19925.58, 22166.24, 22949.06]</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>[18993.4, 19062.1, 18775.5]</t>
+          <t>[19921.5, 19866.6, 21013.7]</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1427,22 +1427,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>5393.03</v>
+        <v>9440.76</v>
       </c>
       <c r="G22" t="n">
-        <v>5389.81</v>
+        <v>9040.290000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>12.57</v>
+        <v>19.19</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>[38541.77, 34725.47, 39661.62]</t>
+          <t>[37818.52, 36080.59, 38388.12]</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>[43730.7, 40363.1, 45004.5]</t>
+          <t>[43050.1, 46554.1, 49803.9]</t>
         </is>
       </c>
     </row>
@@ -1454,17 +1454,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>(1, 1, 1)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1473,22 +1473,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2939.16</v>
+        <v>5300.91</v>
       </c>
       <c r="G23" t="n">
-        <v>2901.76</v>
+        <v>4890.46</v>
       </c>
       <c r="H23" t="n">
-        <v>6.82</v>
+        <v>9.81</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>[37682.98, 41452.62, 44292.58]</t>
+          <t>[42680.14, 46750.31, 43985.66]</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>[40363.1, 45004.5, 41819.3]</t>
+          <t>[46554.1, 49803.9, 51729.5]</t>
         </is>
       </c>
     </row>
@@ -1500,17 +1500,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>(1, 1, 1)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1519,22 +1519,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2446.89</v>
+        <v>3225.91</v>
       </c>
       <c r="G24" t="n">
-        <v>1912.52</v>
+        <v>2775.74</v>
       </c>
       <c r="H24" t="n">
-        <v>4.48</v>
+        <v>5.56</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>[43371.39, 45725.1, 43101.95]</t>
+          <t>[50468.12, 47056.14, 50388.24]</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>[45004.5, 41819.3, 42903.3]</t>
+          <t>[49803.9, 51729.5, 47398.6]</t>
         </is>
       </c>
     </row>
@@ -1546,17 +1546,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>(1, 1, 1)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1565,22 +1565,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>5691.73</v>
+        <v>3750.01</v>
       </c>
       <c r="G25" t="n">
-        <v>5583.72</v>
+        <v>3554.62</v>
       </c>
       <c r="H25" t="n">
-        <v>12.97</v>
+        <v>7.49</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>[48515.67, 46982.92, 38629.21]</t>
+          <t>[46509.47, 49874.25, 44478.7]</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>[41819.3, 42903.3, 44604.4]</t>
+          <t>[51729.5, 47398.6, 41510.5]</t>
         </is>
       </c>
     </row>
@@ -1592,17 +1592,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>(1, 1, 1)</t>
+          <t>(2, 0, 1)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1611,22 +1611,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>5318.81</v>
+        <v>5956.81</v>
       </c>
       <c r="G26" t="n">
-        <v>4381.44</v>
+        <v>5778.11</v>
       </c>
       <c r="H26" t="n">
-        <v>10.31</v>
+        <v>13.41</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>[42015.94, 36358.68, 34657.36]</t>
+          <t>[54570.87, 47890.66, 42702.0]</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>[42903.3, 44604.4, 38668.6]</t>
+          <t>[47398.6, 41510.5, 38920.1]</t>
         </is>
       </c>
     </row>
@@ -1638,17 +1638,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>(1, 1, 1)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1657,22 +1657,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>8910.1</v>
+        <v>1137.53</v>
       </c>
       <c r="G27" t="n">
-        <v>8713.59</v>
+        <v>1073.74</v>
       </c>
       <c r="H27" t="n">
-        <v>20.52</v>
+        <v>2.64</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>[35047.74, 32535.67, 32598.92]</t>
+          <t>[42422.14, 38203.36, 42617.54]</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>[44604.4, 38668.6, 43050.1]</t>
+          <t>[41510.5, 38920.1, 41024.7]</t>
         </is>
       </c>
     </row>
@@ -1684,17 +1684,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>(1, 1, 1)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1703,22 +1703,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>6104.88</v>
+        <v>2886.46</v>
       </c>
       <c r="G28" t="n">
-        <v>5014.9</v>
+        <v>2342.47</v>
       </c>
       <c r="H28" t="n">
-        <v>11.2</v>
+        <v>5.84</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>[39898.02, 38868.82, 36920.09]</t>
+          <t>[37474.69, 41901.75, 45035.75]</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>[38668.6, 43050.1, 46554.1]</t>
+          <t>[38920.1, 41024.7, 40330.8]</t>
         </is>
       </c>
     </row>
@@ -1730,17 +1730,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>(1, 1, 1)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1749,22 +1749,22 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>9440.76</v>
+        <v>3981.89</v>
       </c>
       <c r="G29" t="n">
-        <v>9040.290000000001</v>
+        <v>3545.45</v>
       </c>
       <c r="H29" t="n">
-        <v>19.19</v>
+        <v>8.65</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>[37818.52, 36080.59, 38388.12]</t>
+          <t>[43328.04, 46439.14, 45000.16]</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>[43050.1, 46554.1, 49803.9]</t>
+          <t>[41024.7, 40330.8, 42775.5]</t>
         </is>
       </c>
     </row>
@@ -1776,12 +1776,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1795,22 +1795,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>5300.91</v>
+        <v>2297.52</v>
       </c>
       <c r="G30" t="n">
-        <v>4890.46</v>
+        <v>1640.11</v>
       </c>
       <c r="H30" t="n">
-        <v>9.81</v>
+        <v>4.08</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>[42680.14, 46750.31, 43985.66]</t>
+          <t>[44240.89, 43145.15, 37439.53]</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>[46554.1, 49803.9, 51729.5]</t>
+          <t>[40330.8, 42775.5, 38080.1]</t>
         </is>
       </c>
     </row>
@@ -1822,12 +1822,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1841,22 +1841,22 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3225.91</v>
+        <v>2326.6</v>
       </c>
       <c r="G31" t="n">
-        <v>2775.74</v>
+        <v>2213.45</v>
       </c>
       <c r="H31" t="n">
-        <v>5.56</v>
+        <v>5.66</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>[50468.12, 47056.14, 50388.24]</t>
+          <t>[39917.24, 35511.76, 33024.35]</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>[49803.9, 51729.5, 47398.6]</t>
+          <t>[42775.5, 38080.1, 34238.1]</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1887,22 +1887,22 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1230.14</v>
+        <v>1392.42</v>
       </c>
       <c r="G32" t="n">
-        <v>1144.3</v>
+        <v>1384.32</v>
       </c>
       <c r="H32" t="n">
-        <v>66.18000000000001</v>
+        <v>42.02</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>[2369.71, 2729.82, 3505.88]</t>
+          <t>[2082.77, 1962.05, 1691.11]</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>[1750.4, 1637.7, 1784.4]</t>
+          <t>[3327.4, 3278.0, 3283.5]</t>
         </is>
       </c>
     </row>
@@ -1914,41 +1914,41 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>(2, 1, 2)</t>
+          <t>(1, 0, 2)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>(1, 1, 1, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>4976.76</v>
+        <v>559.9</v>
       </c>
       <c r="G33" t="n">
-        <v>4636.73</v>
+        <v>448.86</v>
       </c>
       <c r="H33" t="n">
-        <v>268.18</v>
+        <v>14.15</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>[3732.51, 7452.89, 7859.29]</t>
+          <t>[3445.72, 3023.83, 4042.89]</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>[1637.7, 1784.4, 1712.4]</t>
+          <t>[3278.0, 3283.5, 3123.7]</t>
         </is>
       </c>
     </row>
@@ -1960,17 +1960,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>(1, 1, 0)</t>
+          <t>(1, 0, 2)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1979,22 +1979,22 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>242.74</v>
+        <v>969.4</v>
       </c>
       <c r="G34" t="n">
-        <v>230.89</v>
+        <v>861.0700000000001</v>
       </c>
       <c r="H34" t="n">
-        <v>12.93</v>
+        <v>25.32</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>[1992.48, 1865.09, 1490.71]</t>
+          <t>[2839.27, 3784.41, 5059.39]</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>[1784.4, 1712.4, 1822.6]</t>
+          <t>[3283.5, 3123.7, 3581.1]</t>
         </is>
       </c>
     </row>
@@ -2006,17 +2006,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>(1, 1, 0)</t>
+          <t>(1, 0, 2)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2025,22 +2025,22 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>688.71</v>
+        <v>1630.79</v>
       </c>
       <c r="G35" t="n">
-        <v>559.62</v>
+        <v>1496.32</v>
       </c>
       <c r="H35" t="n">
-        <v>31.34</v>
+        <v>41.75</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>[1627.32, 1295.59, 706.94]</t>
+          <t>[4463.31, 5938.29, 5581.66]</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>[1712.4, 1822.6, 1773.7]</t>
+          <t>[3123.7, 3581.1, 4789.5]</t>
         </is>
       </c>
     </row>
@@ -2052,17 +2052,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>(1, 1, 0)</t>
+          <t>(1, 0, 2)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2071,22 +2071,22 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1119.68</v>
+        <v>930.72</v>
       </c>
       <c r="G36" t="n">
-        <v>1015.69</v>
+        <v>765.17</v>
       </c>
       <c r="H36" t="n">
-        <v>49.66</v>
+        <v>16.78</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>[1382.76, 760.55, 759.81]</t>
+          <t>[3645.89, 3443.44, 3448.73]</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>[1822.6, 1773.7, 2353.9]</t>
+          <t>[3581.1, 4789.5, 4333.4]</t>
         </is>
       </c>
     </row>
@@ -2098,17 +2098,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>(1, 1, 0)</t>
+          <t>(1, 0, 2)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2117,22 +2117,22 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1637.97</v>
+        <v>1124.29</v>
       </c>
       <c r="G37" t="n">
-        <v>1459.18</v>
+        <v>1102.23</v>
       </c>
       <c r="H37" t="n">
-        <v>54.93</v>
+        <v>23.83</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>[1099.46, 1109.33, 868.68]</t>
+          <t>[3374.02, 3378.74, 3764.76]</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>[1773.7, 2353.9, 3327.4]</t>
+          <t>[4789.5, 4333.4, 4701.3]</t>
         </is>
       </c>
     </row>
@@ -2144,17 +2144,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>(1, 1, 0)</t>
+          <t>(2, 0, 0)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2163,22 +2163,22 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1422.72</v>
+        <v>1013.86</v>
       </c>
       <c r="G38" t="n">
-        <v>1282.62</v>
+        <v>1008.43</v>
       </c>
       <c r="H38" t="n">
-        <v>40.52</v>
+        <v>22.42</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>[1941.07, 1643.42, 1526.96]</t>
+          <t>[5194.15, 5773.56, 5536.4]</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>[2353.9, 3327.4, 3278.0]</t>
+          <t>[4333.4, 4701.3, 4444.1]</t>
         </is>
       </c>
     </row>
@@ -2190,17 +2190,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>(1, 1, 0)</t>
+          <t>(2, 0, 0)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2209,22 +2209,22 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1392.42</v>
+        <v>220.43</v>
       </c>
       <c r="G39" t="n">
-        <v>1384.32</v>
+        <v>169.51</v>
       </c>
       <c r="H39" t="n">
-        <v>42.02</v>
+        <v>3.77</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>[2082.77, 1962.05, 1691.11]</t>
+          <t>[4606.1, 4397.58, 4080.9]</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>[3327.4, 3278.0, 3283.5]</t>
+          <t>[4701.3, 4444.1, 4447.7]</t>
         </is>
       </c>
     </row>
@@ -2236,41 +2236,41 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>(1, 0, 2)</t>
+          <t>(3, 0, 2)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(2, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>559.9</v>
+        <v>177.09</v>
       </c>
       <c r="G40" t="n">
-        <v>448.86</v>
+        <v>157.6</v>
       </c>
       <c r="H40" t="n">
-        <v>14.15</v>
+        <v>3.64</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>[3445.72, 3023.83, 4042.89]</t>
+          <t>[4514.58, 4712.81, 4220.52]</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>[3278.0, 3283.5, 3123.7]</t>
+          <t>[4444.1, 4447.7, 4083.3]</t>
         </is>
       </c>
     </row>
@@ -2282,41 +2282,41 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>(1, 0, 2)</t>
+          <t>(3, 0, 2)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(2, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>969.4</v>
+        <v>141.05</v>
       </c>
       <c r="G41" t="n">
-        <v>861.0700000000001</v>
+        <v>134.59</v>
       </c>
       <c r="H41" t="n">
-        <v>25.32</v>
+        <v>3.24</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>[2839.27, 3784.41, 5059.39]</t>
+          <t>[4627.05, 4161.32, 3736.7]</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>[3283.5, 3123.7, 3581.1]</t>
+          <t>[4447.7, 4083.3, 3883.1]</t>
         </is>
       </c>
     </row>
@@ -2328,12 +2328,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2347,22 +2347,22 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>344.44</v>
+        <v>270.35</v>
       </c>
       <c r="G42" t="n">
-        <v>310.39</v>
+        <v>269.07</v>
       </c>
       <c r="H42" t="n">
-        <v>8.460000000000001</v>
+        <v>5.07</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>[3049.99, 3345.84, 5001.76]</t>
+          <t>[5683.36, 5319.85, 4387.49]</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>[2905.2, 3066.1, 4495.1]</t>
+          <t>[5916.0, 5600.6, 4681.3]</t>
         </is>
       </c>
     </row>
@@ -2374,12 +2374,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2393,22 +2393,22 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>189.47</v>
+        <v>255.57</v>
       </c>
       <c r="G43" t="n">
-        <v>163.49</v>
+        <v>216.8</v>
       </c>
       <c r="H43" t="n">
-        <v>4.02</v>
+        <v>4.7</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>[3199.88, 4787.87, 5411.82]</t>
+          <t>[5501.19, 4536.68, 3987.81]</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>[3066.1, 4495.1, 5347.9]</t>
+          <t>[5600.6, 4681.3, 4394.2]</t>
         </is>
       </c>
     </row>
@@ -2420,12 +2420,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2439,22 +2439,22 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>152.27</v>
+        <v>377.32</v>
       </c>
       <c r="G44" t="n">
-        <v>148.42</v>
+        <v>324.01</v>
       </c>
       <c r="H44" t="n">
-        <v>2.68</v>
+        <v>7.19</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>[4621.02, 5225.08, 6866.73]</t>
+          <t>[4604.59, 4047.6, 4004.37]</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>[4495.1, 5347.9, 6670.2]</t>
+          <t>[4681.3, 4394.2, 4553.1]</t>
         </is>
       </c>
     </row>
@@ -2466,12 +2466,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2485,22 +2485,22 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>641.85</v>
+        <v>382.02</v>
       </c>
       <c r="G45" t="n">
-        <v>455.44</v>
+        <v>371.59</v>
       </c>
       <c r="H45" t="n">
-        <v>6.59</v>
+        <v>10.91</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>[5105.84, 6710.15, 6321.28]</t>
+          <t>[4102.48, 4057.88, 2482.12]</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>[5347.9, 6670.2, 7405.6]</t>
+          <t>[4394.2, 4553.1, 2154.3]</t>
         </is>
       </c>
     </row>
@@ -2512,12 +2512,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2531,22 +2531,22 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>594.41</v>
+        <v>315.63</v>
       </c>
       <c r="G46" t="n">
-        <v>554.26</v>
+        <v>282.97</v>
       </c>
       <c r="H46" t="n">
-        <v>8.15</v>
+        <v>10.55</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>[6973.63, 6577.64, 5556.91]</t>
+          <t>[4299.28, 2621.22, 2792.63]</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>[6670.2, 7405.6, 6088.3]</t>
+          <t>[4553.1, 2154.3, 2920.8]</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2577,22 +2577,22 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>901.58</v>
+        <v>504.56</v>
       </c>
       <c r="G47" t="n">
-        <v>891.1900000000001</v>
+        <v>414.08</v>
       </c>
       <c r="H47" t="n">
-        <v>13.74</v>
+        <v>15.02</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>[6340.6, 5356.72, 5039.0]</t>
+          <t>[2748.77, 2928.02, 4361.54]</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>[7405.6, 6088.3, 5916.0]</t>
+          <t>[2154.3, 2920.8, 3721.0]</t>
         </is>
       </c>
     </row>
@@ -2604,12 +2604,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2619,26 +2619,26 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>(2, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>156.75</v>
+        <v>335.73</v>
       </c>
       <c r="G48" t="n">
-        <v>152.63</v>
+        <v>275.35</v>
       </c>
       <c r="H48" t="n">
-        <v>2.63</v>
+        <v>7.96</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>[6201.08, 5770.23, 5401.25]</t>
+          <t>[2461.23, 3710.66, 4169.15]</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>[6088.3, 5916.0, 5600.6]</t>
+          <t>[2920.8, 3721.0, 4525.3]</t>
         </is>
       </c>
     </row>
@@ -2650,12 +2650,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2665,26 +2665,26 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>(2, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>270.35</v>
+        <v>358.69</v>
       </c>
       <c r="G49" t="n">
-        <v>269.07</v>
+        <v>325.25</v>
       </c>
       <c r="H49" t="n">
-        <v>5.07</v>
+        <v>7.66</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>[5683.36, 5319.85, 4387.49]</t>
+          <t>[4258.91, 4763.95, 6327.29]</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>[5916.0, 5600.6, 4681.3]</t>
+          <t>[3721.0, 4525.3, 6128.1]</t>
         </is>
       </c>
     </row>
@@ -2696,12 +2696,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2711,26 +2711,26 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>(2, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>255.57</v>
+        <v>308.59</v>
       </c>
       <c r="G50" t="n">
-        <v>216.8</v>
+        <v>294.96</v>
       </c>
       <c r="H50" t="n">
-        <v>4.7</v>
+        <v>5.18</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>[5501.19, 4536.68, 3987.81]</t>
+          <t>[4318.1, 5708.24, 6033.07]</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>[5600.6, 4681.3, 4394.2]</t>
+          <t>[4525.3, 6128.1, 6290.9]</t>
         </is>
       </c>
     </row>
@@ -2742,12 +2742,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2757,26 +2757,26 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>(2, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>377.32</v>
+        <v>488.83</v>
       </c>
       <c r="G51" t="n">
-        <v>324.01</v>
+        <v>361.99</v>
       </c>
       <c r="H51" t="n">
-        <v>7.19</v>
+        <v>5.94</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>[4604.59, 4047.6, 4004.37]</t>
+          <t>[5908.17, 6240.94, 5260.31]</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>[4681.3, 4394.2, 4553.1]</t>
+          <t>[6128.1, 6290.9, 6076.4]</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2803,26 +2803,26 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>9.390000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="G52" t="n">
-        <v>6.51</v>
+        <v>1.19</v>
       </c>
       <c r="H52" t="n">
-        <v>38.03</v>
+        <v>7.71</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>[33.23, 19.47, 15.66]</t>
+          <t>[16.75, 16.65, 16.47]</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>[17.2, 16.9, 16.6]</t>
+          <t>[15.7, 15.5, 15.1]</t>
         </is>
       </c>
     </row>
@@ -2834,12 +2834,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2849,26 +2849,26 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="G53" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="H53" t="n">
-        <v>8.619999999999999</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>[17.87, 14.79, 17.7]</t>
+          <t>[16.64, 16.46, 16.36]</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>[16.9, 16.6, 16.2]</t>
+          <t>[15.5, 15.1, 15.0]</t>
         </is>
       </c>
     </row>
@@ -2880,12 +2880,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2895,26 +2895,26 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="G54" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="H54" t="n">
-        <v>6.77</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>[14.79, 17.69, 16.13]</t>
+          <t>[16.44, 16.35, 16.07]</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>[16.6, 16.2, 16.1]</t>
+          <t>[15.1, 15.0, 15.1]</t>
         </is>
       </c>
     </row>
@@ -2926,12 +2926,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2941,26 +2941,26 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>6.68</v>
+        <v>1.16</v>
       </c>
       <c r="G55" t="n">
-        <v>4.34</v>
+        <v>1.15</v>
       </c>
       <c r="H55" t="n">
-        <v>27.37</v>
+        <v>7.67</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>[17.71, 16.13, 27.27]</t>
+          <t>[16.34, 16.06, 16.06]</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>[16.2, 16.1, 15.8]</t>
+          <t>[15.0, 15.1, 14.9]</t>
         </is>
       </c>
     </row>
@@ -2972,12 +2972,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2987,26 +2987,26 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>6.61</v>
+        <v>0.99</v>
       </c>
       <c r="G56" t="n">
-        <v>3.85</v>
+        <v>0.98</v>
       </c>
       <c r="H56" t="n">
-        <v>24.4</v>
+        <v>6.58</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>[16.12, 27.24, 15.69]</t>
+          <t>[16.04, 16.04, 15.76]</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>[16.1, 15.8, 15.8]</t>
+          <t>[15.1, 14.9, 14.9]</t>
         </is>
       </c>
     </row>
@@ -3018,12 +3018,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3033,26 +3033,26 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>6.62</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G57" t="n">
-        <v>3.9</v>
+        <v>0.92</v>
       </c>
       <c r="H57" t="n">
-        <v>24.69</v>
+        <v>6.21</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>[27.27, 15.69, 15.58]</t>
+          <t>[16.04, 15.76, 15.48]</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>[15.8, 15.8, 15.7]</t>
+          <t>[14.9, 14.9, 14.7]</t>
         </is>
       </c>
     </row>
@@ -3064,12 +3064,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3083,22 +3083,22 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1.09</v>
+        <v>0.74</v>
       </c>
       <c r="G58" t="n">
-        <v>1.09</v>
+        <v>0.73</v>
       </c>
       <c r="H58" t="n">
-        <v>6.96</v>
+        <v>4.99</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>[16.85, 16.76, 16.66]</t>
+          <t>[15.75, 15.47, 15.09]</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>[15.8, 15.7, 15.5]</t>
+          <t>[14.9, 14.7, 14.5]</t>
         </is>
       </c>
     </row>
@@ -3110,12 +3110,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3129,22 +3129,22 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1.2</v>
+        <v>0.68</v>
       </c>
       <c r="G59" t="n">
-        <v>1.19</v>
+        <v>0.68</v>
       </c>
       <c r="H59" t="n">
-        <v>7.71</v>
+        <v>4.68</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>[16.75, 16.65, 16.47]</t>
+          <t>[15.46, 15.09, 14.99]</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>[15.7, 15.5, 15.1]</t>
+          <t>[14.7, 14.5, 14.3]</t>
         </is>
       </c>
     </row>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3175,22 +3175,22 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1.29</v>
+        <v>0.59</v>
       </c>
       <c r="G60" t="n">
-        <v>1.29</v>
+        <v>0.59</v>
       </c>
       <c r="H60" t="n">
-        <v>8.470000000000001</v>
+        <v>4.12</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>[16.64, 16.46, 16.36]</t>
+          <t>[15.08, 14.99, 14.71]</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>[15.5, 15.1, 15.0]</t>
+          <t>[14.5, 14.3, 14.2]</t>
         </is>
       </c>
     </row>
@@ -3202,12 +3202,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3221,22 +3221,22 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1.23</v>
+        <v>0.63</v>
       </c>
       <c r="G61" t="n">
-        <v>1.22</v>
+        <v>0.63</v>
       </c>
       <c r="H61" t="n">
-        <v>8.109999999999999</v>
+        <v>4.43</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>[16.44, 16.35, 16.07]</t>
+          <t>[14.98, 14.7, 14.7]</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>[15.1, 15.0, 15.1]</t>
+          <t>[14.3, 14.2, 14.0]</t>
         </is>
       </c>
     </row>
@@ -3248,12 +3248,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3267,22 +3267,22 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>0.24</v>
+        <v>0.19</v>
       </c>
       <c r="G62" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="H62" t="n">
-        <v>102.59</v>
+        <v>179.52</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>[0.52, 0.47, 0.23]</t>
+          <t>[0.35, 0.24, 0.24]</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>[0.2, 0.2, 0.2]</t>
+          <t>[0.1, 0.1, 0.1]</t>
         </is>
       </c>
     </row>
@@ -3294,12 +3294,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3313,22 +3313,22 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="G63" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="H63" t="n">
-        <v>56.66</v>
+        <v>98.64</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>[0.39, 0.2, 0.34]</t>
+          <t>[0.2, 0.2, 0.2]</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>[0.2, 0.2, 0.2]</t>
+          <t>[0.1, 0.1, 0.1]</t>
         </is>
       </c>
     </row>
@@ -3340,12 +3340,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3362,19 +3362,19 @@
         <v>0.09</v>
       </c>
       <c r="G64" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="H64" t="n">
-        <v>39.65</v>
+        <v>85.31</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>[0.17, 0.31, 0.31]</t>
+          <t>[0.18, 0.18, 0.0]</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>[0.2, 0.2, 0.2]</t>
+          <t>[0.1, 0.1, 0.1]</t>
         </is>
       </c>
     </row>
@@ -3386,12 +3386,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3405,22 +3405,22 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>0.14</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G65" t="n">
-        <v>0.14</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H65" t="n">
-        <v>67.81999999999999</v>
+        <v>62.43</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>[0.31, 0.31, 0.38]</t>
+          <t>[0.16, 0.0, 0.25]</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>[0.2, 0.2, 0.2]</t>
+          <t>[0.1, 0.1, 0.2]</t>
         </is>
       </c>
     </row>
@@ -3432,12 +3432,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3451,22 +3451,22 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>0.15</v>
+        <v>0.09</v>
       </c>
       <c r="G66" t="n">
-        <v>0.15</v>
+        <v>0.08</v>
       </c>
       <c r="H66" t="n">
-        <v>73.68000000000001</v>
+        <v>77.34</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>[0.29, 0.35, 0.0]</t>
+          <t>[0.0, 0.23, 0.22]</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>[0.2, 0.2, 0.2]</t>
+          <t>[0.1, 0.2, 0.1]</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3497,22 +3497,22 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="G67" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="H67" t="n">
-        <v>102.16</v>
+        <v>189.52</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>[0.33, 0.0, 0.24]</t>
+          <t>[0.4, 0.36, 0.31]</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>[0.2, 0.2, 0.1]</t>
+          <t>[0.2, 0.1, 0.1]</t>
         </is>
       </c>
     </row>
@@ -3524,12 +3524,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3543,22 +3543,22 @@
         </is>
       </c>
       <c r="F68" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="G68" t="n">
         <v>0.14</v>
       </c>
-      <c r="G68" t="n">
-        <v>0.12</v>
-      </c>
       <c r="H68" t="n">
-        <v>91.48</v>
+        <v>137.86</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>[0.0, 0.22, 0.15]</t>
+          <t>[0.32, 0.28, 0.32]</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>[0.2, 0.1, 0.1]</t>
+          <t>[0.1, 0.1, 0.3]</t>
         </is>
       </c>
     </row>
@@ -3570,12 +3570,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3589,22 +3589,22 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>0.19</v>
+        <v>0.13</v>
       </c>
       <c r="G69" t="n">
-        <v>0.18</v>
+        <v>0.11</v>
       </c>
       <c r="H69" t="n">
-        <v>179.52</v>
+        <v>106.37</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>[0.35, 0.24, 0.24]</t>
+          <t>[0.24, 0.27, 0.27]</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>[0.1, 0.1, 0.1]</t>
+          <t>[0.1, 0.3, 0.1]</t>
         </is>
       </c>
     </row>
@@ -3616,12 +3616,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3635,22 +3635,22 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="G70" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="H70" t="n">
-        <v>98.64</v>
+        <v>57.43</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>[0.2, 0.2, 0.2]</t>
+          <t>[0.24, 0.24, 0.26]</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>[0.1, 0.1, 0.1]</t>
+          <t>[0.3, 0.1, 0.3]</t>
         </is>
       </c>
     </row>
@@ -3662,12 +3662,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3684,19 +3684,19 @@
         <v>0.09</v>
       </c>
       <c r="G71" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="H71" t="n">
-        <v>85.31</v>
+        <v>55.13</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>[0.18, 0.18, 0.0]</t>
+          <t>[0.25, 0.27, 0.22]</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>[0.1, 0.1, 0.1]</t>
+          <t>[0.1, 0.3, 0.2]</t>
         </is>
       </c>
     </row>
@@ -3708,17 +3708,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>(1, 0, 2)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3727,22 +3727,22 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>941.37</v>
+        <v>1960.68</v>
       </c>
       <c r="G72" t="n">
-        <v>747.09</v>
+        <v>1803.53</v>
       </c>
       <c r="H72" t="n">
-        <v>5.25</v>
+        <v>11.84</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>[14026.81, 12859.68, 13211.12]</t>
+          <t>[13765.77, 12660.22, 13289.33]</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>[14208.6, 14391.8, 13738.5]</t>
+          <t>[14567.7, 14597.2, 15961.0]</t>
         </is>
       </c>
     </row>
@@ -3754,12 +3754,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3773,22 +3773,22 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>1070.19</v>
+        <v>2704.32</v>
       </c>
       <c r="G73" t="n">
-        <v>896.7</v>
+        <v>2479.87</v>
       </c>
       <c r="H73" t="n">
-        <v>6.34</v>
+        <v>15.07</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>[13193.97, 13658.57, 12546.05]</t>
+          <t>[13342.19, 13656.17, 13615.82]</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>[14391.8, 13738.5, 13958.4]</t>
+          <t>[14597.2, 15961.0, 17495.6]</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3819,22 +3819,22 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>1220.94</v>
+        <v>2534.25</v>
       </c>
       <c r="G74" t="n">
-        <v>1190.73</v>
+        <v>2367.89</v>
       </c>
       <c r="H74" t="n">
-        <v>8.19</v>
+        <v>13.81</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>[14933.51, 13100.39, 14114.93]</t>
+          <t>[14820.26, 14207.87, 14590.88]</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>[13738.5, 13958.4, 15634.1]</t>
+          <t>[15961.0, 17495.6, 17266.1]</t>
         </is>
       </c>
     </row>
@@ -3846,41 +3846,41 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>(0, 0, 4)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>1691.6</v>
+        <v>2108.71</v>
       </c>
       <c r="G75" t="n">
-        <v>1630.5</v>
+        <v>2105.49</v>
       </c>
       <c r="H75" t="n">
-        <v>11.15</v>
+        <v>12.44</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>[12562.53, 14399.3, 12272.08]</t>
+          <t>[15248.99, 15157.29, 14031.95]</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>[13958.4, 15634.1, 14532.9]</t>
+          <t>[17495.6, 17266.1, 15993.0]</t>
         </is>
       </c>
     </row>
@@ -3892,41 +3892,41 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>(0, 0, 4)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(2, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>886.09</v>
+        <v>459.26</v>
       </c>
       <c r="G76" t="n">
-        <v>652.16</v>
+        <v>358.56</v>
       </c>
       <c r="H76" t="n">
-        <v>4.51</v>
+        <v>2.25</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>[15761.93, 13041.01, 14130.16]</t>
+          <t>[17545.09, 16046.7, 14765.61]</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>[15634.1, 14532.9, 13793.4]</t>
+          <t>[17266.1, 15993.0, 15508.6]</t>
         </is>
       </c>
     </row>
@@ -3938,41 +3938,41 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>(0, 0, 4)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>(2, 1, 0, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1159.82</v>
+        <v>2100.22</v>
       </c>
       <c r="G77" t="n">
-        <v>805.37</v>
+        <v>1387.59</v>
       </c>
       <c r="H77" t="n">
-        <v>5.56</v>
+        <v>7.52</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>[12549.63, 13642.35, 14285.91]</t>
+          <t>[15970.17, 14965.5, 15413.15]</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>[14532.9, 13793.4, 14567.7]</t>
+          <t>[15993.0, 15508.6, 19010.0]</t>
         </is>
       </c>
     </row>
@@ -3984,41 +3984,41 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>(2, 1, 0, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>1225.71</v>
+        <v>3319.05</v>
       </c>
       <c r="G78" t="n">
-        <v>1160.15</v>
+        <v>2861.95</v>
       </c>
       <c r="H78" t="n">
-        <v>8.16</v>
+        <v>15.55</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>[15343.04, 15185.5, 13284.19]</t>
+          <t>[14970.0, 15421.71, 13886.73]</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>[13793.4, 14567.7, 14597.2]</t>
+          <t>[15508.6, 19010.0, 18345.7]</t>
         </is>
       </c>
     </row>
@@ -4030,41 +4030,41 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(1, 0, 2)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>(2, 1, 0, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>1960.68</v>
+        <v>4115.01</v>
       </c>
       <c r="G79" t="n">
-        <v>1803.53</v>
+        <v>4055.27</v>
       </c>
       <c r="H79" t="n">
-        <v>11.84</v>
+        <v>21</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>[13765.77, 12660.22, 13289.33]</t>
+          <t>[15819.91, 14271.17, 15522.72]</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>[14567.7, 14597.2, 15961.0]</t>
+          <t>[19010.0, 18345.7, 20423.9]</t>
         </is>
       </c>
     </row>
@@ -4076,41 +4076,41 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>(2, 1, 0, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>2704.32</v>
+        <v>4534.62</v>
       </c>
       <c r="G80" t="n">
-        <v>2479.87</v>
+        <v>3990.26</v>
       </c>
       <c r="H80" t="n">
-        <v>15.07</v>
+        <v>19.63</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>[13342.19, 13656.17, 13615.82]</t>
+          <t>[16412.21, 17351.59, 13951.32]</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>[14597.2, 15961.0, 17495.6]</t>
+          <t>[18345.7, 20423.9, 20916.3]</t>
         </is>
       </c>
     </row>
@@ -4122,41 +4122,41 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>(2, 1, 0, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>2534.25</v>
+        <v>4504.19</v>
       </c>
       <c r="G81" t="n">
-        <v>2367.89</v>
+        <v>4054.52</v>
       </c>
       <c r="H81" t="n">
-        <v>13.81</v>
+        <v>19.09</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>[14820.26, 14207.87, 14590.88]</t>
+          <t>[19129.38, 15237.51, 16641.75]</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>[15961.0, 17495.6, 17266.1]</t>
+          <t>[20423.9, 20916.3, 21832.0]</t>
         </is>
       </c>
     </row>
@@ -4168,17 +4168,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -4187,22 +4187,22 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>1670.06</v>
+        <v>3450.88</v>
       </c>
       <c r="G82" t="n">
-        <v>1307.3</v>
+        <v>3423.86</v>
       </c>
       <c r="H82" t="n">
-        <v>17.97</v>
+        <v>30.86</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>[8289.19, 7413.49, 10299.93]</t>
+          <t>[18563.81, 14716.63, 11432.12]</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>[8077.7, 6406.5, 7596.5]</t>
+          <t>[14534.9, 11659.5, 8246.6]</t>
         </is>
       </c>
     </row>
@@ -4214,12 +4214,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4233,22 +4233,22 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>2178.49</v>
+        <v>1335.42</v>
       </c>
       <c r="G83" t="n">
-        <v>2020.72</v>
+        <v>1203.39</v>
       </c>
       <c r="H83" t="n">
-        <v>26.03</v>
+        <v>15.24</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>[7276.42, 10169.03, 11168.19]</t>
+          <t>[12070.56, 9667.34, 8905.37]</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>[6406.5, 7596.5, 8548.5]</t>
+          <t>[11659.5, 8246.6, 7127.0]</t>
         </is>
       </c>
     </row>
@@ -4260,12 +4260,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4279,22 +4279,22 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1481.61</v>
+        <v>1757.79</v>
       </c>
       <c r="G84" t="n">
-        <v>1373.95</v>
+        <v>1693.21</v>
       </c>
       <c r="H84" t="n">
-        <v>16.32</v>
+        <v>23.21</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>[9257.7, 10410.68, 10668.34]</t>
+          <t>[9412.3, 8729.52, 9311.91]</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>[7596.5, 8548.5, 11266.8]</t>
+          <t>[8246.6, 7127.0, 7000.5]</t>
         </is>
       </c>
     </row>
@@ -4306,12 +4306,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4321,26 +4321,26 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>1930.17</v>
+        <v>2161.22</v>
       </c>
       <c r="G85" t="n">
-        <v>1615.82</v>
+        <v>1966.61</v>
       </c>
       <c r="H85" t="n">
-        <v>12.85</v>
+        <v>35.44</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>[8671.21, 8909.29, 12251.18]</t>
+          <t>[7955.3, 9053.42, 7636.51]</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>[8548.5, 11266.8, 14618.4]</t>
+          <t>[7127.0, 7000.5, 4617.9]</t>
         </is>
       </c>
     </row>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4367,26 +4367,26 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>3005.87</v>
+        <v>1990.09</v>
       </c>
       <c r="G86" t="n">
-        <v>2932.69</v>
+        <v>1926.68</v>
       </c>
       <c r="H86" t="n">
-        <v>19.88</v>
+        <v>39.91</v>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>[8810.26, 12141.77, 14639.39]</t>
+          <t>[8321.29, 7159.26, 6102.29]</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>[11266.8, 14618.4, 18504.3]</t>
+          <t>[7000.5, 4617.9, 4184.4]</t>
         </is>
       </c>
     </row>
@@ -4398,41 +4398,41 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>2023.51</v>
+        <v>1348.24</v>
       </c>
       <c r="G87" t="n">
-        <v>1608</v>
+        <v>1326.29</v>
       </c>
       <c r="H87" t="n">
-        <v>10.74</v>
+        <v>27.71</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>[15459.29, 17862.55, 17876.28]</t>
+          <t>[6250.99, 5489.4, 7318.78]</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>[14618.4, 18504.3, 14534.9]</t>
+          <t>[4617.9, 4184.4, 6278.0]</t>
         </is>
       </c>
     </row>
@@ -4444,41 +4444,41 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>2306.45</v>
+        <v>287.43</v>
       </c>
       <c r="G88" t="n">
-        <v>2234.11</v>
+        <v>243.58</v>
       </c>
       <c r="H88" t="n">
-        <v>16.03</v>
+        <v>3.93</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>[17050.93, 17348.03, 14095.31]</t>
+          <t>[4233.79, 5855.81, 6955.17]</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>[18504.3, 14534.9, 11659.5]</t>
+          <t>[4184.4, 6278.0, 6696.0]</t>
         </is>
       </c>
     </row>
@@ -4490,41 +4490,41 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>3450.88</v>
+        <v>655.33</v>
       </c>
       <c r="G89" t="n">
-        <v>3423.86</v>
+        <v>561.6</v>
       </c>
       <c r="H89" t="n">
-        <v>30.86</v>
+        <v>8.33</v>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>[18563.81, 14716.63, 11432.12]</t>
+          <t>[5792.37, 6887.23, 8007.14]</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>[14534.9, 11659.5, 8246.6]</t>
+          <t>[6278.0, 6696.0, 6999.2]</t>
         </is>
       </c>
     </row>
@@ -4536,12 +4536,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4551,26 +4551,26 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>1335.42</v>
+        <v>1131.1</v>
       </c>
       <c r="G90" t="n">
-        <v>1203.39</v>
+        <v>1083.32</v>
       </c>
       <c r="H90" t="n">
-        <v>15.24</v>
+        <v>13.83</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>[12070.56, 9667.34, 8905.37]</t>
+          <t>[7377.86, 8477.75, 11780.04]</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>[11659.5, 8246.6, 7127.0]</t>
+          <t>[6696.0, 6999.2, 10690.5]</t>
         </is>
       </c>
     </row>
@@ -4582,41 +4582,41 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(2, 0, 2)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(1, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>1757.79</v>
+        <v>484.91</v>
       </c>
       <c r="G91" t="n">
-        <v>1693.21</v>
+        <v>404.53</v>
       </c>
       <c r="H91" t="n">
-        <v>23.21</v>
+        <v>4.8</v>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>[9412.3, 8729.52, 9311.91]</t>
+          <t>[7759.86, 10806.9, 13473.48]</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>[8246.6, 7127.0, 7000.5]</t>
+          <t>[6999.2, 10690.5, 13810.0]</t>
         </is>
       </c>
     </row>
@@ -4628,12 +4628,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4647,22 +4647,22 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>731.05</v>
+        <v>892.38</v>
       </c>
       <c r="G92" t="n">
-        <v>538.01</v>
+        <v>870.71</v>
       </c>
       <c r="H92" t="n">
-        <v>4.42</v>
+        <v>6.96</v>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>[9913.77, 10795.12, 11725.78]</t>
+          <t>[11961.13, 12136.65, 10360.7]</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>[9718.4, 10614.4, 12963.7]</t>
+          <t>[12949.8, 13164.9, 10955.9]</t>
         </is>
       </c>
     </row>
@@ -4674,12 +4674,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4693,22 +4693,22 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>772.5</v>
+        <v>703.4</v>
       </c>
       <c r="G93" t="n">
-        <v>517.3</v>
+        <v>652.9299999999999</v>
       </c>
       <c r="H93" t="n">
-        <v>4.06</v>
+        <v>5.43</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>[10726.67, 11635.04, 12728.25]</t>
+          <t>[12459.14, 10646.55, 10692.93]</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>[10614.4, 12963.7, 12617.3]</t>
+          <t>[13164.9, 10955.9, 11636.6]</t>
         </is>
       </c>
     </row>
@@ -4720,12 +4720,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4739,22 +4739,22 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>1043.89</v>
+        <v>505.29</v>
       </c>
       <c r="G94" t="n">
-        <v>879.26</v>
+        <v>433.56</v>
       </c>
       <c r="H94" t="n">
-        <v>6.94</v>
+        <v>3.88</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>[11604.09, 12706.95, 13555.21]</t>
+          <t>[10835.85, 10881.09, 10104.88]</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>[12963.7, 12617.3, 12366.7]</t>
+          <t>[10955.9, 11636.6, 10530.0]</t>
         </is>
       </c>
     </row>
@@ -4766,12 +4766,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4785,22 +4785,22 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>1673.03</v>
+        <v>605.0599999999999</v>
       </c>
       <c r="G95" t="n">
-        <v>1540.94</v>
+        <v>587.8099999999999</v>
       </c>
       <c r="H95" t="n">
-        <v>12.11</v>
+        <v>5.8</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>[13265.98, 14154.55, 15254.5]</t>
+          <t>[10933.28, 10144.33, 9437.85]</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>[12617.3, 12366.7, 13068.2]</t>
+          <t>[11636.6, 10530.0, 8763.4]</t>
         </is>
       </c>
     </row>
@@ -4812,12 +4812,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>1595</v>
+        <v>553.36</v>
       </c>
       <c r="G96" t="n">
-        <v>1567.64</v>
+        <v>415.45</v>
       </c>
       <c r="H96" t="n">
-        <v>12.6</v>
+        <v>4.55</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>[13881.66, 15019.56, 12898.6]</t>
+          <t>[10349.55, 9695.1, 10493.72]</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>[12366.7, 13068.2, 11662.0]</t>
+          <t>[10530.0, 8763.4, 10359.5]</t>
         </is>
       </c>
     </row>
@@ -4858,12 +4858,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4877,22 +4877,22 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>984.4400000000001</v>
+        <v>936.72</v>
       </c>
       <c r="G97" t="n">
-        <v>892.53</v>
+        <v>818.83</v>
       </c>
       <c r="H97" t="n">
-        <v>7.08</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>[14515.6, 12443.96, 12501.57]</t>
+          <t>[9756.82, 10554.76, 11726.99]</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>[13068.2, 11662.0, 12949.8]</t>
+          <t>[8763.4, 10359.5, 10459.2]</t>
         </is>
       </c>
     </row>
@@ -4904,12 +4904,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4923,22 +4923,22 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>749.95</v>
+        <v>760.85</v>
       </c>
       <c r="G98" t="n">
-        <v>706.75</v>
+        <v>664.24</v>
       </c>
       <c r="H98" t="n">
-        <v>5.52</v>
+        <v>6.17</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>[12014.5, 12082.43, 12264.53]</t>
+          <t>[10217.12, 11336.98, 12109.07]</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>[11662.0, 12949.8, 13164.9]</t>
+          <t>[10359.5, 10459.2, 11136.5]</t>
         </is>
       </c>
     </row>
@@ -4950,12 +4950,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4969,22 +4969,22 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>892.38</v>
+        <v>1530.98</v>
       </c>
       <c r="G99" t="n">
-        <v>870.71</v>
+        <v>1406.71</v>
       </c>
       <c r="H99" t="n">
-        <v>6.96</v>
+        <v>13.22</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>[11961.13, 12136.65, 10360.7]</t>
+          <t>[11386.61, 12170.27, 12767.97]</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>[12949.8, 13164.9, 10955.9]</t>
+          <t>[10459.2, 11136.5, 10509.0]</t>
         </is>
       </c>
     </row>
@@ -4996,12 +4996,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5015,22 +5015,22 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>703.4</v>
+        <v>1207.33</v>
       </c>
       <c r="G100" t="n">
-        <v>652.9299999999999</v>
+        <v>1009.82</v>
       </c>
       <c r="H100" t="n">
-        <v>5.43</v>
+        <v>9.24</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>[12459.14, 10646.55, 10692.93]</t>
+          <t>[11850.82, 12435.58, 13426.18]</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>[13164.9, 10955.9, 11636.6]</t>
+          <t>[11136.5, 10509.0, 13037.6]</t>
         </is>
       </c>
     </row>
@@ -5042,12 +5042,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5061,22 +5061,22 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>505.29</v>
+        <v>944.58</v>
       </c>
       <c r="G101" t="n">
-        <v>433.56</v>
+        <v>609.1</v>
       </c>
       <c r="H101" t="n">
-        <v>3.88</v>
+        <v>5.72</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>[10835.85, 10881.09, 10104.88]</t>
+          <t>[12139.07, 13128.57, 11352.05]</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>[10955.9, 11636.6, 10530.0]</t>
+          <t>[10509.0, 13037.6, 11245.8]</t>
         </is>
       </c>
     </row>
@@ -5088,41 +5088,41 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>(3, 0, 2)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>(1, 1, 1, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>1869.85</v>
+        <v>2814.62</v>
       </c>
       <c r="G102" t="n">
-        <v>1549.18</v>
+        <v>2384.84</v>
       </c>
       <c r="H102" t="n">
-        <v>2.92</v>
+        <v>4.88</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>[52360.61, 49127.11, 56192.56]</t>
+          <t>[54470.12, 51994.83, 52210.08]</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>[53229.8, 52155.5, 56942.5]</t>
+          <t>[54175.0, 48842.0, 48503.5]</t>
         </is>
       </c>
     </row>
@@ -5134,41 +5134,41 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(3, 0, 1)</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>(1, 1, 1, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>2036.42</v>
+        <v>3950.48</v>
       </c>
       <c r="G103" t="n">
-        <v>1731.86</v>
+        <v>3869.9</v>
       </c>
       <c r="H103" t="n">
-        <v>3.29</v>
+        <v>8.07</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>[49798.78, 56718.32, 55262.79]</t>
+          <t>[51846.42, 52186.91, 51916.98]</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>[52155.5, 56942.5, 52648.1]</t>
+          <t>[48842.0, 48503.5, 46995.1]</t>
         </is>
       </c>
     </row>
@@ -5180,17 +5180,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -5199,22 +5199,22 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>5078.54</v>
+        <v>1601.36</v>
       </c>
       <c r="G104" t="n">
-        <v>4699.4</v>
+        <v>1489.95</v>
       </c>
       <c r="H104" t="n">
-        <v>8.76</v>
+        <v>3.06</v>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>[59249.21, 57418.24, 60379.76]</t>
+          <t>[49221.66, 49135.27, 52700.13]</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>[56942.5, 52648.1, 53358.4]</t>
+          <t>[48503.5, 46995.1, 51088.6]</t>
         </is>
       </c>
     </row>
@@ -5226,17 +5226,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(3, 0, 2)</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -5245,22 +5245,22 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>5201.57</v>
+        <v>2716.12</v>
       </c>
       <c r="G105" t="n">
-        <v>4911.93</v>
+        <v>2398.89</v>
       </c>
       <c r="H105" t="n">
-        <v>9.25</v>
+        <v>4.82</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>[55394.78, 58416.07, 59991.74]</t>
+          <t>[48693.04, 52400.82, 46414.58]</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>[52648.1, 53358.4, 53060.3]</t>
+          <t>[46995.1, 51088.6, 50601.1]</t>
         </is>
       </c>
     </row>
@@ -5272,41 +5272,41 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>(3, 0, 0)</t>
+          <t>(3, 0, 1)</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>(1, 1, 1, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F106" t="n">
-        <v>4628.74</v>
+        <v>3262.91</v>
       </c>
       <c r="G106" t="n">
-        <v>4411.25</v>
+        <v>2380.72</v>
       </c>
       <c r="H106" t="n">
-        <v>8.24</v>
+        <v>4.82</v>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>[55878.0, 57902.09, 59910.85]</t>
+          <t>[50386.69, 45067.03, 42811.77]</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>[53358.4, 53060.3, 54038.5]</t>
+          <t>[51088.6, 50601.1, 41905.6]</t>
         </is>
       </c>
     </row>
@@ -5318,41 +5318,41 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>(2, 0, 2)</t>
+          <t>(2, 0, 1)</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>(1, 1, 1, 12)</t>
+          <t>(0, 1, 2, 12)</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>3089.1</v>
+        <v>3401.75</v>
       </c>
       <c r="G107" t="n">
-        <v>3024.96</v>
+        <v>3104.55</v>
       </c>
       <c r="H107" t="n">
-        <v>5.62</v>
+        <v>6.5</v>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>[55200.18, 57533.69, 57614.8]</t>
+          <t>[45697.79, 43422.38, 49710.45]</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>[53060.3, 54038.5, 54175.0]</t>
+          <t>[50601.1, 41905.6, 46816.9]</t>
         </is>
       </c>
     </row>
@@ -5364,12 +5364,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -5379,26 +5379,26 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>2842.33</v>
+        <v>5638.72</v>
       </c>
       <c r="G108" t="n">
-        <v>2500.69</v>
+        <v>5117.96</v>
       </c>
       <c r="H108" t="n">
-        <v>4.91</v>
+        <v>11.28</v>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>[55440.65, 55871.05, 53245.85]</t>
+          <t>[48186.0, 54071.91, 52554.95]</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>[54038.5, 54175.0, 48842.0]</t>
+          <t>[41905.6, 46816.9, 54373.4]</t>
         </is>
       </c>
     </row>
@@ -5410,41 +5410,41 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(3, 0, 2)</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(1, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>2814.62</v>
+        <v>4909.58</v>
       </c>
       <c r="G109" t="n">
-        <v>2384.84</v>
+        <v>4417.27</v>
       </c>
       <c r="H109" t="n">
-        <v>4.88</v>
+        <v>8.34</v>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>[54470.12, 51994.83, 52210.08]</t>
+          <t>[48992.17, 47069.47, 50471.09]</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>[54175.0, 48842.0, 48503.5]</t>
+          <t>[46816.9, 54373.4, 54243.7]</t>
         </is>
       </c>
     </row>
@@ -5456,17 +5456,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>(3, 0, 1)</t>
+          <t>(2, 0, 2)</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -5475,22 +5475,22 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>3950.48</v>
+        <v>5650.46</v>
       </c>
       <c r="G110" t="n">
-        <v>3869.9</v>
+        <v>5504.37</v>
       </c>
       <c r="H110" t="n">
-        <v>8.07</v>
+        <v>10.04</v>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>[51846.42, 52186.91, 51916.98]</t>
+          <t>[47080.67, 49847.09, 51218.42]</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>[48842.0, 48503.5, 46995.1]</t>
+          <t>[54373.4, 54243.7, 56042.2]</t>
         </is>
       </c>
     </row>
@@ -5502,41 +5502,41 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(2, 0, 1)</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>(1, 1, 1, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>1601.36</v>
+        <v>2818.5</v>
       </c>
       <c r="G111" t="n">
-        <v>1489.95</v>
+        <v>2290.47</v>
       </c>
       <c r="H111" t="n">
-        <v>3.06</v>
+        <v>4.18</v>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>[49221.66, 49135.27, 52700.13]</t>
+          <t>[56423.01, 56378.98, 59340.14]</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>[48503.5, 46995.1, 51088.6]</t>
+          <t>[54243.7, 56042.2, 54984.8]</t>
         </is>
       </c>
     </row>
@@ -5548,17 +5548,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(3, 0, 2)</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -5567,22 +5567,22 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>6813.31</v>
+        <v>3336.41</v>
       </c>
       <c r="G112" t="n">
-        <v>6026.8</v>
+        <v>2295.36</v>
       </c>
       <c r="H112" t="n">
-        <v>17.62</v>
+        <v>6.85</v>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>[25634.88, 25076.05, 35791.08]</t>
+          <t>[33263.1, 33891.82, 27668.19]</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>[35614.2, 30979.0, 37989.2]</t>
+          <t>[34474.8, 33915.9, 33318.5]</t>
         </is>
       </c>
     </row>
@@ -5594,17 +5594,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>(0, 1, 3)</t>
+          <t>(3, 0, 2)</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -5613,22 +5613,22 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>9141.85</v>
+        <v>3545.7</v>
       </c>
       <c r="G113" t="n">
-        <v>7733.1</v>
+        <v>3162.24</v>
       </c>
       <c r="H113" t="n">
-        <v>22.08</v>
+        <v>9.42</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>[31945.12, 47959.12, 45508.66]</t>
+          <t>[35349.61, 28020.2, 36608.61]</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>[30979.0, 37989.2, 33245.4]</t>
+          <t>[33915.9, 33318.5, 33853.9]</t>
         </is>
       </c>
     </row>
@@ -5640,17 +5640,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>(0, 1, 3)</t>
+          <t>(3, 0, 2)</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -5659,22 +5659,22 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>13163.07</v>
+        <v>6017.83</v>
       </c>
       <c r="G114" t="n">
-        <v>12727.61</v>
+        <v>5571.87</v>
       </c>
       <c r="H114" t="n">
-        <v>42.45</v>
+        <v>17.18</v>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>[47160.66, 45025.87, 42657.92]</t>
+          <t>[27521.29, 36535.56, 39649.63]</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>[37989.2, 33245.4, 25427.0]</t>
+          <t>[33318.5, 33853.9, 31412.9]</t>
         </is>
       </c>
     </row>
@@ -5686,17 +5686,17 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>(0, 1, 3)</t>
+          <t>(3, 0, 2)</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -5705,22 +5705,22 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>8447.690000000001</v>
+        <v>9195.719999999999</v>
       </c>
       <c r="G115" t="n">
-        <v>7822.41</v>
+        <v>7609.59</v>
       </c>
       <c r="H115" t="n">
-        <v>28.37</v>
+        <v>23.49</v>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>[36907.22, 36838.77, 37132.62]</t>
+          <t>[42860.03, 44530.7, 33975.55]</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>[33245.4, 25427.0, 28739.0]</t>
+          <t>[33853.9, 31412.9, 33270.7]</t>
         </is>
       </c>
     </row>
@@ -5732,17 +5732,17 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>(0, 1, 3)</t>
+          <t>(3, 0, 2)</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -5751,22 +5751,22 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>6055.49</v>
+        <v>4780.12</v>
       </c>
       <c r="G116" t="n">
-        <v>5230.74</v>
+        <v>4382.05</v>
       </c>
       <c r="H116" t="n">
-        <v>19.3</v>
+        <v>14.76</v>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>[33922.46, 34780.47, 34344.19]</t>
+          <t>[38407.53, 30787.88, 28866.7]</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>[25427.0, 28739.0, 33188.9]</t>
+          <t>[31412.9, 33270.7, 25198.0]</t>
         </is>
       </c>
     </row>
@@ -5778,17 +5778,17 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>(2, 1, 2)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -5797,22 +5797,22 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>4720.03</v>
+        <v>5087.33</v>
       </c>
       <c r="G117" t="n">
-        <v>4122.71</v>
+        <v>4215.87</v>
       </c>
       <c r="H117" t="n">
-        <v>12.35</v>
+        <v>13.7</v>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>[29936.65, 28830.8, 27662.41]</t>
+          <t>[26264.69, 25504.35, 33678.54]</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>[28739.0, 33188.9, 34474.8]</t>
+          <t>[33270.7, 25198.0, 28343.3]</t>
         </is>
       </c>
     </row>
@@ -5824,17 +5824,17 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>(3, 1, 3)</t>
+          <t>(4, 0, 0)</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -5843,22 +5843,22 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>5562.42</v>
+        <v>4896.8</v>
       </c>
       <c r="G118" t="n">
-        <v>5496.63</v>
+        <v>4237.03</v>
       </c>
       <c r="H118" t="n">
-        <v>16.2</v>
+        <v>15.34</v>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>[28355.91, 27774.0, 28959.79]</t>
+          <t>[29608.82, 35496.21, 33731.14]</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>[33188.9, 34474.8, 33915.9]</t>
+          <t>[25198.0, 28343.3, 34878.5]</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -5885,26 +5885,26 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(1, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>3336.41</v>
+        <v>6179.45</v>
       </c>
       <c r="G119" t="n">
-        <v>2295.36</v>
+        <v>5223.64</v>
       </c>
       <c r="H119" t="n">
-        <v>6.85</v>
+        <v>16.36</v>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>[33263.1, 33891.82, 27668.19]</t>
+          <t>[35169.78, 34253.91, 27225.45]</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>[34474.8, 33915.9, 33318.5]</t>
+          <t>[28343.3, 34878.5, 35445.3]</t>
         </is>
       </c>
     </row>
@@ -5916,17 +5916,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>(3, 0, 2)</t>
+          <t>(4, 0, 0)</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -5935,22 +5935,22 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>3545.7</v>
+        <v>8568.690000000001</v>
       </c>
       <c r="G120" t="n">
-        <v>3162.24</v>
+        <v>8313.559999999999</v>
       </c>
       <c r="H120" t="n">
-        <v>9.42</v>
+        <v>23.99</v>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>[35349.61, 28020.2, 36608.61]</t>
+          <t>[28559.28, 24269.68, 25907.67]</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>[33915.9, 33318.5, 33853.9]</t>
+          <t>[34878.5, 35445.3, 33353.5]</t>
         </is>
       </c>
     </row>
@@ -5962,17 +5962,17 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>(3, 0, 2)</t>
+          <t>(4, 0, 0)</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -5981,22 +5981,22 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>6017.83</v>
+        <v>5274.23</v>
       </c>
       <c r="G121" t="n">
-        <v>5571.87</v>
+        <v>4892.4</v>
       </c>
       <c r="H121" t="n">
-        <v>17.18</v>
+        <v>14.33</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>[27521.29, 36535.56, 39649.63]</t>
+          <t>[28128.38, 28484.18, 34688.26]</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>[33318.5, 33853.9, 31412.9]</t>
+          <t>[35445.3, 33353.5, 32197.3]</t>
         </is>
       </c>
     </row>
@@ -6008,12 +6008,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -6027,22 +6027,22 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>55.24</v>
+        <v>14.51</v>
       </c>
       <c r="G122" t="n">
-        <v>52.69</v>
+        <v>12.37</v>
       </c>
       <c r="H122" t="n">
-        <v>16.7</v>
+        <v>1.61</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>[337.62, 377.82, 387.55]</t>
+          <t>[798.9, 860.81, 768.31]</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>[307.6, 308.7, 328.6]</t>
+          <t>[784.7, 863.1, 747.7]</t>
         </is>
       </c>
     </row>
@@ -6054,12 +6054,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -6073,22 +6073,22 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>30.56</v>
+        <v>10.8</v>
       </c>
       <c r="G123" t="n">
-        <v>25.39</v>
+        <v>8.73</v>
       </c>
       <c r="H123" t="n">
-        <v>7.92</v>
+        <v>1.08</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>[349.48, 362.31, 590.08]</t>
+          <t>[847.99, 758.73, 671.06]</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>[308.7, 328.6, 588.4]</t>
+          <t>[863.1, 747.7, 671.1]</t>
         </is>
       </c>
     </row>
@@ -6100,12 +6100,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -6119,22 +6119,22 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>30.96</v>
+        <v>19.23</v>
       </c>
       <c r="G124" t="n">
-        <v>24.4</v>
+        <v>17.97</v>
       </c>
       <c r="H124" t="n">
-        <v>4.19</v>
+        <v>2.52</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>[326.17, 539.51, 598.62]</t>
+          <t>[770.02, 679.41, 719.08]</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>[328.6, 588.4, 620.5]</t>
+          <t>[747.7, 671.1, 695.8]</t>
         </is>
       </c>
     </row>
@@ -6146,12 +6146,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -6161,26 +6161,26 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>(2, 1, 1, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F125" t="n">
-        <v>70.43000000000001</v>
+        <v>32.02</v>
       </c>
       <c r="G125" t="n">
-        <v>54.14</v>
+        <v>23.66</v>
       </c>
       <c r="H125" t="n">
-        <v>7.03</v>
+        <v>7.79</v>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>[561.98, 638.83, 743.83]</t>
+          <t>[662.9, 704.42, 313.17]</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>[588.4, 620.5, 861.5]</t>
+          <t>[671.1, 695.8, 259.0]</t>
         </is>
       </c>
     </row>
@@ -6192,12 +6192,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -6211,22 +6211,22 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>72.5</v>
+        <v>36.41</v>
       </c>
       <c r="G126" t="n">
-        <v>53.12</v>
+        <v>31.62</v>
       </c>
       <c r="H126" t="n">
-        <v>6.57</v>
+        <v>10.15</v>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>[644.38, 738.9, 784.41]</t>
+          <t>[711.66, 315.91, 334.62]</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>[620.5, 861.5, 797.3]</t>
+          <t>[695.8, 259.0, 356.7]</t>
         </is>
       </c>
     </row>
@@ -6238,12 +6238,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -6253,26 +6253,26 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>(2, 1, 1, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F127" t="n">
-        <v>79.48</v>
+        <v>55.54</v>
       </c>
       <c r="G127" t="n">
-        <v>58.03</v>
+        <v>51.71</v>
       </c>
       <c r="H127" t="n">
-        <v>6.89</v>
+        <v>15.11</v>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>[728.07, 804.96, 817.71]</t>
+          <t>[310.07, 329.51, 350.34]</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>[861.5, 797.3, 784.7]</t>
+          <t>[259.0, 356.7, 427.2]</t>
         </is>
       </c>
     </row>
@@ -6284,12 +6284,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -6303,22 +6303,22 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>86.77</v>
+        <v>115.31</v>
       </c>
       <c r="G128" t="n">
-        <v>85.94</v>
+        <v>111.66</v>
       </c>
       <c r="H128" t="n">
-        <v>10.62</v>
+        <v>23.11</v>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>[892.4, 878.38, 932.15]</t>
+          <t>[283.43, 308.12, 539.08]</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>[797.3, 784.7, 863.1]</t>
+          <t>[356.7, 427.2, 681.7]</t>
         </is>
       </c>
     </row>
@@ -6330,12 +6330,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6349,22 +6349,22 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>14.51</v>
+        <v>56.93</v>
       </c>
       <c r="G129" t="n">
-        <v>12.37</v>
+        <v>56.52</v>
       </c>
       <c r="H129" t="n">
-        <v>1.61</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>[798.9, 860.81, 768.31]</t>
+          <t>[373.11, 631.99, 671.74]</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>[784.7, 863.1, 747.7]</t>
+          <t>[427.2, 681.7, 737.5]</t>
         </is>
       </c>
     </row>
@@ -6376,12 +6376,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -6395,22 +6395,22 @@
         </is>
       </c>
       <c r="F130" t="n">
-        <v>10.8</v>
+        <v>43.2</v>
       </c>
       <c r="G130" t="n">
-        <v>8.73</v>
+        <v>31.94</v>
       </c>
       <c r="H130" t="n">
-        <v>1.08</v>
+        <v>4.04</v>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>[847.99, 758.73, 671.06]</t>
+          <t>[706.94, 737.35, 908.25]</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>[863.1, 747.7, 671.1]</t>
+          <t>[681.7, 737.5, 837.8]</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6441,22 +6441,22 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>19.23</v>
+        <v>41.98</v>
       </c>
       <c r="G131" t="n">
-        <v>17.97</v>
+        <v>40.01</v>
       </c>
       <c r="H131" t="n">
-        <v>2.52</v>
+        <v>4.97</v>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>[770.02, 679.41, 719.08]</t>
+          <t>[715.38, 885.3, 859.32]</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>[747.7, 671.1, 695.8]</t>
+          <t>[737.5, 837.8, 808.9]</t>
         </is>
       </c>
     </row>
@@ -6468,41 +6468,41 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>(0, 1, 0)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>5.74</v>
+        <v>1.17</v>
       </c>
       <c r="G132" t="n">
-        <v>4.36</v>
+        <v>1.1</v>
       </c>
       <c r="H132" t="n">
-        <v>11.91</v>
+        <v>1.72</v>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>[33.48, 24.51, 32.33]</t>
+          <t>[62.78, 64.13, 69.56]</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>[33.7, 28.1, 41.6]</t>
+          <t>[64.1, 62.7, 69.0]</t>
         </is>
       </c>
     </row>
@@ -6514,41 +6514,41 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>(0, 1, 0)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F133" t="n">
-        <v>10.51</v>
+        <v>2.13</v>
       </c>
       <c r="G133" t="n">
-        <v>9.32</v>
+        <v>2.09</v>
       </c>
       <c r="H133" t="n">
-        <v>20.28</v>
+        <v>3.53</v>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>[24.62, 32.51, 42.43]</t>
+          <t>[65.37, 70.79, 50.31]</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>[28.1, 41.6, 57.8]</t>
+          <t>[62.7, 69.0, 48.5]</t>
         </is>
       </c>
     </row>
@@ -6560,41 +6560,41 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>(0, 1, 0)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>8.210000000000001</v>
+        <v>0.67</v>
       </c>
       <c r="G134" t="n">
-        <v>7.87</v>
+        <v>0.57</v>
       </c>
       <c r="H134" t="n">
-        <v>14.66</v>
+        <v>1.09</v>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>[37.04, 48.45, 47.9]</t>
+          <t>[68.13, 48.57, 40.34]</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>[41.6, 57.8, 57.6]</t>
+          <t>[69.0, 48.5, 41.1]</t>
         </is>
       </c>
     </row>
@@ -6606,41 +6606,41 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>(0, 1, 0)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>9.33</v>
+        <v>1.06</v>
       </c>
       <c r="G135" t="n">
-        <v>7.6</v>
+        <v>0.88</v>
       </c>
       <c r="H135" t="n">
-        <v>9.58</v>
+        <v>2.56</v>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>[54.26, 53.62, 82.04]</t>
+          <t>[49.14, 40.78, 31.88]</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>[57.8, 57.6, 97.3]</t>
+          <t>[48.5, 41.1, 30.2]</t>
         </is>
       </c>
     </row>
@@ -6652,41 +6652,41 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>(0, 1, 0)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>5.75</v>
+        <v>2.23</v>
       </c>
       <c r="G136" t="n">
-        <v>3.61</v>
+        <v>1.89</v>
       </c>
       <c r="H136" t="n">
-        <v>3.83</v>
+        <v>6.68</v>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>[57.11, 87.36, 93.01]</t>
+          <t>[40.28, 31.53, 29.44]</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>[57.6, 97.3, 93.4]</t>
+          <t>[41.1, 30.2, 25.9]</t>
         </is>
       </c>
     </row>
@@ -6698,41 +6698,41 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>(0, 1, 0)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F137" t="n">
-        <v>5.42</v>
+        <v>3.28</v>
       </c>
       <c r="G137" t="n">
-        <v>3.56</v>
+        <v>3.16</v>
       </c>
       <c r="H137" t="n">
-        <v>3.84</v>
+        <v>10.4</v>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>[87.97, 93.78, 65.08]</t>
+          <t>[32.11, 29.94, 41.41]</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>[97.3, 93.4, 64.1]</t>
+          <t>[30.2, 25.9, 37.9]</t>
         </is>
       </c>
     </row>
@@ -6744,41 +6744,41 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>(0, 1, 0)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(2, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>9.93</v>
+        <v>2.29</v>
       </c>
       <c r="G138" t="n">
-        <v>9.81</v>
+        <v>2.22</v>
       </c>
       <c r="H138" t="n">
-        <v>13.77</v>
+        <v>6.15</v>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>[103.63, 71.9, 74.1]</t>
+          <t>[28.31, 39.32, 55.02]</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>[93.4, 64.1, 62.7]</t>
+          <t>[25.9, 37.9, 52.2]</t>
         </is>
       </c>
     </row>
@@ -6790,12 +6790,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -6809,22 +6809,22 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>1.17</v>
+        <v>1.98</v>
       </c>
       <c r="G139" t="n">
-        <v>1.1</v>
+        <v>1.86</v>
       </c>
       <c r="H139" t="n">
-        <v>1.72</v>
+        <v>3.9</v>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>[62.78, 64.13, 69.56]</t>
+          <t>[36.24, 51.05, 51.52]</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>[64.1, 62.7, 69.0]</t>
+          <t>[37.9, 52.2, 54.3]</t>
         </is>
       </c>
     </row>
@@ -6836,12 +6836,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -6855,22 +6855,22 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>2.13</v>
+        <v>1.75</v>
       </c>
       <c r="G140" t="n">
-        <v>2.09</v>
+        <v>1.51</v>
       </c>
       <c r="H140" t="n">
-        <v>3.53</v>
+        <v>2.17</v>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>[65.37, 70.79, 50.31]</t>
+          <t>[53.19, 53.5, 90.75]</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>[62.7, 69.0, 48.5]</t>
+          <t>[52.2, 54.3, 88.0]</t>
         </is>
       </c>
     </row>
@@ -6882,12 +6882,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -6901,22 +6901,22 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>0.67</v>
+        <v>1.26</v>
       </c>
       <c r="G141" t="n">
-        <v>0.57</v>
+        <v>1.09</v>
       </c>
       <c r="H141" t="n">
-        <v>1.09</v>
+        <v>1.64</v>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>[68.13, 48.57, 40.34]</t>
+          <t>[52.58, 89.33, 87.57]</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>[69.0, 48.5, 41.1]</t>
+          <t>[54.3, 88.0, 87.8]</t>
         </is>
       </c>
     </row>
@@ -6928,41 +6928,41 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>(3, 0, 1)</t>
+          <t>(0, 0, 1)</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>974.5</v>
+        <v>586.1</v>
       </c>
       <c r="G142" t="n">
-        <v>925.22</v>
+        <v>585.4299999999999</v>
       </c>
       <c r="H142" t="n">
-        <v>32.56</v>
+        <v>11.31</v>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>[3350.18, 4186.09, 5091.08]</t>
+          <t>[5691.55, 4891.72, 3608.84]</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>[2308.2, 2958.4, 4585.1]</t>
+          <t>[6256.2, 5516.8, 4175.4]</t>
         </is>
       </c>
     </row>
@@ -6974,41 +6974,41 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>(3, 0, 3)</t>
+          <t>(0, 0, 1)</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>452.45</v>
+        <v>468.99</v>
       </c>
       <c r="G143" t="n">
-        <v>350.77</v>
+        <v>458.39</v>
       </c>
       <c r="H143" t="n">
-        <v>8.609999999999999</v>
+        <v>11.46</v>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>[3298.25, 4591.45, 5676.92]</t>
+          <t>[5198.41, 3640.45, 2782.86]</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>[2958.4, 4585.1, 4970.8]</t>
+          <t>[5516.8, 4175.4, 3304.7]</t>
         </is>
       </c>
     </row>
@@ -7020,41 +7020,41 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>(2, 0, 3)</t>
+          <t>(0, 0, 1)</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>822.01</v>
+        <v>429.44</v>
       </c>
       <c r="G144" t="n">
-        <v>770.28</v>
+        <v>400.49</v>
       </c>
       <c r="H144" t="n">
-        <v>14.62</v>
+        <v>10.38</v>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>[3494.41, 4576.48, 5974.77]</t>
+          <t>[4549.37, 3530.01, 3314.71]</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>[4585.1, 4970.8, 6800.6]</t>
+          <t>[4175.4, 3304.7, 3916.9]</t>
         </is>
       </c>
     </row>
@@ -7066,41 +7066,41 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>(4, 0, 0)</t>
+          <t>(0, 0, 1)</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>745.11</v>
+        <v>409.74</v>
       </c>
       <c r="G145" t="n">
-        <v>555.24</v>
+        <v>298.82</v>
       </c>
       <c r="H145" t="n">
-        <v>8.369999999999999</v>
+        <v>8.25</v>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>[4803.95, 7042.89, 8159.09]</t>
+          <t>[3155.17, 3225.36, 2204.39]</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>[4970.8, 6800.6, 6902.5]</t>
+          <t>[3304.7, 3916.9, 2149.0]</t>
         </is>
       </c>
     </row>
@@ -7112,41 +7112,41 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>(4, 0, 0)</t>
+          <t>(0, 1, 0)</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>822.3</v>
+        <v>281.55</v>
       </c>
       <c r="G146" t="n">
-        <v>574.91</v>
+        <v>215.25</v>
       </c>
       <c r="H146" t="n">
-        <v>8.35</v>
+        <v>8.69</v>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>[7136.48, 8286.59, 7060.08]</t>
+          <t>[3737.63, 2602.32, 3335.37]</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>[6800.6, 6902.5, 7055.3]</t>
+          <t>[3916.9, 2149.0, 3322.2]</t>
         </is>
       </c>
     </row>
@@ -7158,17 +7158,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>(0, 0, 1)</t>
+          <t>(0, 1, 0)</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -7177,22 +7177,22 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>711.6900000000001</v>
+        <v>671.42</v>
       </c>
       <c r="G147" t="n">
-        <v>655.8099999999999</v>
+        <v>581.79</v>
       </c>
       <c r="H147" t="n">
-        <v>9.93</v>
+        <v>18.2</v>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>[7220.94, 6401.83, 5260.66]</t>
+          <t>[2727.13, 3495.34, 5417.28]</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>[6902.5, 7055.3, 6256.2]</t>
+          <t>[2149.0, 3322.2, 4423.2]</t>
         </is>
       </c>
     </row>
@@ -7204,41 +7204,41 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>(0, 0, 1)</t>
+          <t>(0, 1, 0)</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F148" t="n">
-        <v>776.88</v>
+        <v>457.71</v>
       </c>
       <c r="G148" t="n">
-        <v>735.75</v>
+        <v>417.81</v>
       </c>
       <c r="H148" t="n">
-        <v>11.92</v>
+        <v>10.29</v>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>[6565.33, 5178.44, 4877.29]</t>
+          <t>[2754.35, 4268.86, 4627.96]</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>[7055.3, 6256.2, 5516.8]</t>
+          <t>[3322.2, 4423.2, 5159.2]</t>
         </is>
       </c>
     </row>
@@ -7250,17 +7250,17 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>(0, 0, 1)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -7269,22 +7269,22 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>586.1</v>
+        <v>924.0599999999999</v>
       </c>
       <c r="G149" t="n">
-        <v>585.4299999999999</v>
+        <v>732.21</v>
       </c>
       <c r="H149" t="n">
-        <v>11.31</v>
+        <v>13.66</v>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>[5691.55, 4891.72, 3608.84]</t>
+          <t>[4928.48, 5343.06, 7309.9]</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>[6256.2, 5516.8, 4175.4]</t>
+          <t>[4423.2, 5159.2, 5802.4]</t>
         </is>
       </c>
     </row>
@@ -7296,41 +7296,41 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>(0, 0, 1)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>468.99</v>
+        <v>761.8099999999999</v>
       </c>
       <c r="G150" t="n">
-        <v>458.39</v>
+        <v>648.46</v>
       </c>
       <c r="H150" t="n">
-        <v>11.46</v>
+        <v>10.87</v>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>[5198.41, 3640.45, 2782.86]</t>
+          <t>[4996.29, 6944.52, 7196.97]</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>[5516.8, 4175.4, 3304.7]</t>
+          <t>[5159.2, 5802.4, 6556.6]</t>
         </is>
       </c>
     </row>
@@ -7342,17 +7342,17 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>(0, 0, 1)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -7361,22 +7361,22 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>429.44</v>
+        <v>1178.99</v>
       </c>
       <c r="G151" t="n">
-        <v>400.49</v>
+        <v>1036.53</v>
       </c>
       <c r="H151" t="n">
-        <v>10.38</v>
+        <v>16.7</v>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>[4549.37, 3530.01, 3314.71]</t>
+          <t>[7400.15, 7799.55, 7727.1]</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>[4175.4, 3304.7, 3916.9]</t>
+          <t>[5802.4, 6556.6, 7458.2]</t>
         </is>
       </c>
     </row>
@@ -7388,41 +7388,41 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(0, 0, 0)</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>471.73</v>
+        <v>6086.48</v>
       </c>
       <c r="G152" t="n">
-        <v>393.88</v>
+        <v>6039.41</v>
       </c>
       <c r="H152" t="n">
-        <v>1.5</v>
+        <v>21.07</v>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>[26543.53, 26543.53, 26543.53]</t>
+          <t>[21703.59, 22309.99, 23739.59]</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>[26494.8, 25868.7, 27001.6]</t>
+          <t>[27169.4, 29416.8, 29285.2]</t>
         </is>
       </c>
     </row>
@@ -7434,41 +7434,41 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(0, 0, 0)</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F153" t="n">
-        <v>489.28</v>
+        <v>2937.13</v>
       </c>
       <c r="G153" t="n">
-        <v>459.16</v>
+        <v>2537.24</v>
       </c>
       <c r="H153" t="n">
-        <v>1.74</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>[26526.37, 26526.37, 26526.37]</t>
+          <t>[25026.48, 26832.92, 27780.71]</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>[25868.7, 27001.6, 26281.8]</t>
+          <t>[29416.8, 29285.2, 27011.6]</t>
         </is>
       </c>
     </row>
@@ -7480,41 +7480,41 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 0, 0)</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F154" t="n">
-        <v>1685.88</v>
+        <v>3011.84</v>
       </c>
       <c r="G154" t="n">
-        <v>1192.36</v>
+        <v>2803.81</v>
       </c>
       <c r="H154" t="n">
-        <v>4.17</v>
+        <v>10.06</v>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>[26266.07, 26266.07, 26266.07]</t>
+          <t>[27225.36, 25018.89, 23298.13]</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>[27001.6, 26281.8, 29091.9]</t>
+          <t>[29285.2, 27011.6, 27657.0]</t>
         </is>
       </c>
     </row>
@@ -7526,41 +7526,41 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>(0, 1, 1)</t>
+          <t>(1, 1, 0)</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F155" t="n">
-        <v>1853.73</v>
+        <v>3266.86</v>
       </c>
       <c r="G155" t="n">
-        <v>1584.84</v>
+        <v>2763.26</v>
       </c>
       <c r="H155" t="n">
-        <v>5.53</v>
+        <v>10.2</v>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>[26551.09, 26551.09, 26551.09]</t>
+          <t>[31884.03, 30469.62, 24589.07]</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>[26281.8, 29091.9, 28495.5]</t>
+          <t>[27011.6, 27657.0, 25193.8]</t>
         </is>
       </c>
     </row>
@@ -7572,12 +7572,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -7587,26 +7587,26 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>1943.76</v>
+        <v>1809.07</v>
       </c>
       <c r="G156" t="n">
-        <v>1693.89</v>
+        <v>1755.51</v>
       </c>
       <c r="H156" t="n">
-        <v>5.92</v>
+        <v>6.52</v>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>[26448.02, 26448.02, 26448.02]</t>
+          <t>[26505.25, 27365.31, 26718.64]</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>[29091.9, 28495.5, 26057.7]</t>
+          <t>[27657.0, 25193.8, 28661.9]</t>
         </is>
       </c>
     </row>
@@ -7618,17 +7618,17 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -7637,22 +7637,22 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>4268.89</v>
+        <v>2633.25</v>
       </c>
       <c r="G157" t="n">
-        <v>3825.51</v>
+        <v>2236.28</v>
       </c>
       <c r="H157" t="n">
-        <v>14.24</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>[27216.7, 21679.23, 21350.13]</t>
+          <t>[28575.62, 28382.38, 30137.2]</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>[28495.5, 26057.7, 27169.4]</t>
+          <t>[25193.8, 28661.9, 27089.7]</t>
         </is>
       </c>
     </row>
@@ -7664,41 +7664,41 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(0, 1, 1)</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(1, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>5948.23</v>
+        <v>1609.85</v>
       </c>
       <c r="G158" t="n">
-        <v>5812.66</v>
+        <v>1408.65</v>
       </c>
       <c r="H158" t="n">
-        <v>20.93</v>
+        <v>4.84</v>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>[21755.94, 21425.67, 22024.31]</t>
+          <t>[26850.46, 27408.54, 27691.43]</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>[26057.7, 27169.4, 29416.8]</t>
+          <t>[28661.9, 27089.7, 29787.1]</t>
         </is>
       </c>
     </row>
@@ -7710,41 +7710,41 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(1, 1, 0)</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>6086.48</v>
+        <v>1329.82</v>
       </c>
       <c r="G159" t="n">
-        <v>6039.41</v>
+        <v>1247.14</v>
       </c>
       <c r="H159" t="n">
-        <v>21.07</v>
+        <v>4.54</v>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>[21703.59, 22309.99, 23739.59]</t>
+          <t>[28482.37, 29163.8, 28767.56]</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>[27169.4, 29416.8, 29285.2]</t>
+          <t>[27089.7, 29787.1, 27042.1]</t>
         </is>
       </c>
     </row>
@@ -7756,41 +7756,41 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(1, 1, 0)</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>2937.13</v>
+        <v>1113.46</v>
       </c>
       <c r="G160" t="n">
-        <v>2537.24</v>
+        <v>1083.49</v>
       </c>
       <c r="H160" t="n">
-        <v>8.720000000000001</v>
+        <v>3.81</v>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>[25026.48, 26832.92, 27780.71]</t>
+          <t>[28486.79, 27765.18, 29235.87]</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>[29416.8, 29285.2, 27011.6]</t>
+          <t>[29787.1, 27042.1, 28008.8]</t>
         </is>
       </c>
     </row>
@@ -7802,41 +7802,41 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>(1, 0, 0)</t>
+          <t>(1, 1, 0)</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F161" t="n">
-        <v>3011.84</v>
+        <v>2216.94</v>
       </c>
       <c r="G161" t="n">
-        <v>2803.81</v>
+        <v>2090.52</v>
       </c>
       <c r="H161" t="n">
-        <v>10.06</v>
+        <v>7.52</v>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>[27225.36, 25018.89, 23298.13]</t>
+          <t>[28186.77, 30190.38, 25041.88]</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>[29285.2, 27011.6, 27657.0]</t>
+          <t>[27042.1, 28008.8, 27987.2]</t>
         </is>
       </c>
     </row>
@@ -7848,41 +7848,41 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>(1, 0, 1)</t>
+          <t>(0, 0, 0)</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>359.77</v>
+        <v>235.57</v>
       </c>
       <c r="G162" t="n">
-        <v>335.02</v>
+        <v>168.24</v>
       </c>
       <c r="H162" t="n">
-        <v>25.16</v>
+        <v>16.32</v>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>[1725.76, 1725.45, 1725.14]</t>
+          <t>[1004.05, 1683.81, 1361.66]</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>[1343.0, 1259.1, 1569.2]</t>
+          <t>[973.5, 1757.9, 961.6]</t>
         </is>
       </c>
     </row>
@@ -7894,41 +7894,41 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>(2, 1, 1)</t>
+          <t>(0, 0, 0)</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>342.35</v>
+        <v>352.94</v>
       </c>
       <c r="G163" t="n">
-        <v>269.3</v>
+        <v>310.98</v>
       </c>
       <c r="H163" t="n">
-        <v>19.05</v>
+        <v>34.18</v>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>[1295.34, 2117.16, 1380.1]</t>
+          <t>[1680.34, 1358.86, 1264.42]</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>[1259.1, 1569.2, 1156.4]</t>
+          <t>[1757.9, 961.6, 806.3]</t>
         </is>
       </c>
     </row>
@@ -7940,41 +7940,41 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>(2, 1, 1)</t>
+          <t>(0, 0, 0)</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F164" t="n">
-        <v>329.11</v>
+        <v>363.15</v>
       </c>
       <c r="G164" t="n">
-        <v>283.78</v>
+        <v>336.58</v>
       </c>
       <c r="H164" t="n">
-        <v>20.62</v>
+        <v>35.74</v>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>[2079.38, 1383.79, 1288.58]</t>
+          <t>[1362.7, 1267.99, 1927.55]</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>[1569.2, 1156.4, 1174.8]</t>
+          <t>[961.6, 806.3, 1780.6]</t>
         </is>
       </c>
     </row>
@@ -7986,41 +7986,41 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>(0, 1, 0)</t>
+          <t>(0, 0, 0)</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>398.6</v>
+        <v>384.15</v>
       </c>
       <c r="G165" t="n">
-        <v>398.47</v>
+        <v>344.91</v>
       </c>
       <c r="H165" t="n">
-        <v>29.7</v>
+        <v>30.13</v>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>[1569.2, 1569.2, 1569.2]</t>
+          <t>[1242.25, 1888.42, 1130.85]</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>[1156.4, 1174.8, 1957.4]</t>
+          <t>[806.3, 1780.6, 1621.8]</t>
         </is>
       </c>
     </row>
@@ -8032,41 +8032,41 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>(2, 1, 1)</t>
+          <t>(0, 0, 1)</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>(0, 0, 0, 0)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>293.2</v>
+        <v>590.92</v>
       </c>
       <c r="G166" t="n">
-        <v>249.99</v>
+        <v>508.79</v>
       </c>
       <c r="H166" t="n">
-        <v>15.65</v>
+        <v>28.44</v>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>[1338.53, 1492.17, 1189.38]</t>
+          <t>[1644.38, 1103.86, 1034.9]</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>[1174.8, 1957.4, 1310.4]</t>
+          <t>[1780.6, 1621.8, 1907.1]</t>
         </is>
       </c>
     </row>
@@ -8078,17 +8078,17 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(0, 0, 1)</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -8097,22 +8097,22 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>60.09</v>
+        <v>991.67</v>
       </c>
       <c r="G167" t="n">
-        <v>44.81</v>
+        <v>909.9</v>
       </c>
       <c r="H167" t="n">
-        <v>2.89</v>
+        <v>41.76</v>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>[2055.76, 1308.29, 1007.46]</t>
+          <t>[1170.9, 1041.99, 1298.62]</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>[1957.4, 1310.4, 973.5]</t>
+          <t>[1621.8, 1907.1, 2712.3]</t>
         </is>
       </c>
     </row>
@@ -8124,17 +8124,17 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(0, 0, 1)</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -8143,22 +8143,22 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>46.71</v>
+        <v>1082.07</v>
       </c>
       <c r="G168" t="n">
-        <v>37.31</v>
+        <v>1027.94</v>
       </c>
       <c r="H168" t="n">
-        <v>2.63</v>
+        <v>44.78</v>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>[1303.36, 1003.66, 1683.16]</t>
+          <t>[1335.9, 1334.06, 983.12]</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>[1310.4, 973.5, 1757.9]</t>
+          <t>[1907.1, 2712.3, 2117.5]</t>
         </is>
       </c>
     </row>
@@ -8170,17 +8170,17 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(0, 0, 1)</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -8189,22 +8189,22 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>235.57</v>
+        <v>1089.37</v>
       </c>
       <c r="G169" t="n">
-        <v>168.24</v>
+        <v>1083.22</v>
       </c>
       <c r="H169" t="n">
-        <v>16.32</v>
+        <v>46.88</v>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>[1004.05, 1683.81, 1361.66]</t>
+          <t>[1780.12, 1012.9, 1029.02]</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>[973.5, 1757.9, 961.6]</t>
+          <t>[2712.3, 2117.5, 2241.9]</t>
         </is>
       </c>
     </row>
@@ -8216,17 +8216,17 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(2, 0, 2)</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -8235,22 +8235,22 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>352.94</v>
+        <v>2361.08</v>
       </c>
       <c r="G170" t="n">
-        <v>310.98</v>
+        <v>2004.34</v>
       </c>
       <c r="H170" t="n">
-        <v>34.18</v>
+        <v>61.04</v>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>[1680.34, 1358.86, 1264.42]</t>
+          <t>[1288.26, 790.35, 978.58]</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>[1757.9, 961.6, 806.3]</t>
+          <t>[2117.5, 2241.9, 4710.8]</t>
         </is>
       </c>
     </row>
@@ -8262,17 +8262,17 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>(0, 0, 0)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -8281,22 +8281,22 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>363.15</v>
+        <v>1407.97</v>
       </c>
       <c r="G171" t="n">
-        <v>336.58</v>
+        <v>1163.08</v>
       </c>
       <c r="H171" t="n">
-        <v>35.74</v>
+        <v>34.17</v>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>[1362.7, 1267.99, 1927.55]</t>
+          <t>[1798.24, 2442.19, 1470.13]</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>[961.6, 806.3, 1780.6]</t>
+          <t>[2241.9, 4710.8, 2247.1]</t>
         </is>
       </c>
     </row>
@@ -8308,12 +8308,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -8327,22 +8327,22 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>1970.3</v>
+        <v>64.39</v>
       </c>
       <c r="G172" t="n">
-        <v>1934.81</v>
+        <v>54.01</v>
       </c>
       <c r="H172" t="n">
-        <v>12.13</v>
+        <v>0.31</v>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>[14590.64, 13090.7, 14470.72]</t>
+          <t>[18716.5, 18040.05, 16432.01]</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>[16000.7, 15324.7, 16631.1]</t>
+          <t>[18689.8, 18071.9, 16535.5]</t>
         </is>
       </c>
     </row>
@@ -8354,17 +8354,17 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>(2, 1, 2)</t>
+          <t>(1, 1, 1)</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -8373,22 +8373,22 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>1268.57</v>
+        <v>907.25</v>
       </c>
       <c r="G173" t="n">
-        <v>1263.71</v>
+        <v>727.27</v>
       </c>
       <c r="H173" t="n">
-        <v>7.81</v>
+        <v>4.48</v>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>[14020.22, 15256.6, 15634.95]</t>
+          <t>[17832.83, 16076.48, 14415.48]</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>[15324.7, 16631.1, 16747.1]</t>
+          <t>[18071.9, 16535.5, 15899.2]</t>
         </is>
       </c>
     </row>
@@ -8400,12 +8400,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -8419,22 +8419,22 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>742.42</v>
+        <v>853.42</v>
       </c>
       <c r="G174" t="n">
-        <v>617.65</v>
+        <v>719.54</v>
       </c>
       <c r="H174" t="n">
-        <v>3.6</v>
+        <v>4.69</v>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>[16287.54, 16437.6, 16214.11]</t>
+          <t>[16452.69, 14970.07, 15981.56]</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>[16631.1, 16747.1, 17414.0]</t>
+          <t>[16535.5, 15899.2, 14834.9]</t>
         </is>
       </c>
     </row>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -8461,26 +8461,26 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>(0, 1, 2, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F175" t="n">
-        <v>947.65</v>
+        <v>935.79</v>
       </c>
       <c r="G175" t="n">
-        <v>759.6900000000001</v>
+        <v>915.62</v>
       </c>
       <c r="H175" t="n">
-        <v>4.16</v>
+        <v>6</v>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>[16947.47, 16871.38, 17296.33]</t>
+          <t>[15091.91, 16021.96, 16007.61]</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>[16747.1, 17414.0, 18832.4]</t>
+          <t>[15899.2, 14834.9, 15255.1]</t>
         </is>
       </c>
     </row>
@@ -8492,12 +8492,12 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -8511,22 +8511,22 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>1286.67</v>
+        <v>1604.81</v>
       </c>
       <c r="G176" t="n">
-        <v>1208.01</v>
+        <v>1565.25</v>
       </c>
       <c r="H176" t="n">
-        <v>6.56</v>
+        <v>10.9</v>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>[16508.98, 16998.03, 17770.05]</t>
+          <t>[16605.17, 16322.14, 15363.53]</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>[17414.0, 18832.4, 18654.7]</t>
+          <t>[14834.9, 15255.1, 13505.1]</t>
         </is>
       </c>
     </row>
@@ -8538,12 +8538,12 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -8557,22 +8557,22 @@
         </is>
       </c>
       <c r="F177" t="n">
-        <v>698.26</v>
+        <v>1063.97</v>
       </c>
       <c r="G177" t="n">
-        <v>588.46</v>
+        <v>918.4299999999999</v>
       </c>
       <c r="H177" t="n">
-        <v>3.13</v>
+        <v>6.4</v>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>[17713.91, 18366.29, 18331.32]</t>
+          <t>[15012.32, 14460.71, 16330.61]</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>[18832.4, 18654.7, 18689.8]</t>
+          <t>[15255.1, 13505.1, 14773.7]</t>
         </is>
       </c>
     </row>
@@ -8584,17 +8584,17 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>(2, 1, 2)</t>
+          <t>(1, 1, 1)</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -8603,22 +8603,22 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>593.41</v>
+        <v>811.74</v>
       </c>
       <c r="G178" t="n">
-        <v>574.59</v>
+        <v>742.1</v>
       </c>
       <c r="H178" t="n">
-        <v>3.1</v>
+        <v>5.12</v>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>[19403.38, 19278.57, 18458.23]</t>
+          <t>[14338.98, 15864.88, 16331.47]</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>[18654.7, 18689.8, 18071.9]</t>
+          <t>[13505.1, 14773.7, 16632.7]</t>
         </is>
       </c>
     </row>
@@ -8630,12 +8630,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -8649,22 +8649,22 @@
         </is>
       </c>
       <c r="F179" t="n">
-        <v>64.39</v>
+        <v>736</v>
       </c>
       <c r="G179" t="n">
-        <v>54.01</v>
+        <v>641.1799999999999</v>
       </c>
       <c r="H179" t="n">
-        <v>0.31</v>
+        <v>4.1</v>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>[18716.5, 18040.05, 16432.01]</t>
+          <t>[15532.96, 16481.15, 17213.73]</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>[18689.8, 18071.9, 16535.5]</t>
+          <t>[14773.7, 16632.7, 16201.0]</t>
         </is>
       </c>
     </row>
@@ -8676,17 +8676,17 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>(1, 1, 1)</t>
+          <t>(2, 1, 2)</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -8695,22 +8695,22 @@
         </is>
       </c>
       <c r="F180" t="n">
-        <v>907.25</v>
+        <v>829.46</v>
       </c>
       <c r="G180" t="n">
-        <v>727.27</v>
+        <v>779.38</v>
       </c>
       <c r="H180" t="n">
-        <v>4.48</v>
+        <v>4.7</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>[17832.83, 16076.48, 14415.48]</t>
+          <t>[15804.87, 16611.04, 17799.87]</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>[18071.9, 16535.5, 15899.2]</t>
+          <t>[16632.7, 16201.0, 16699.6]</t>
         </is>
       </c>
     </row>
@@ -8722,12 +8722,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -8741,22 +8741,22 @@
         </is>
       </c>
       <c r="F181" t="n">
-        <v>853.42</v>
+        <v>1219.18</v>
       </c>
       <c r="G181" t="n">
-        <v>719.54</v>
+        <v>1004.59</v>
       </c>
       <c r="H181" t="n">
-        <v>4.69</v>
+        <v>6.07</v>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>[16452.69, 14970.07, 15981.56]</t>
+          <t>[17349.79, 18468.86, 18829.93]</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>[16535.5, 15899.2, 14834.9]</t>
+          <t>[16201.0, 16699.6, 18734.2]</t>
         </is>
       </c>
     </row>
@@ -8768,12 +8768,12 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -8787,22 +8787,22 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>5404.71</v>
+        <v>8658.629999999999</v>
       </c>
       <c r="G182" t="n">
-        <v>4430.72</v>
+        <v>7848.34</v>
       </c>
       <c r="H182" t="n">
-        <v>9.41</v>
+        <v>15.7</v>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>[41400.63, 38455.75, 42665.07]</t>
+          <t>[50600.76, 43486.99, 35873.05]</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>[41455.0, 45002.3, 49356.3]</t>
+          <t>[53762.5, 51783.9, 47959.4]</t>
         </is>
       </c>
     </row>
@@ -8814,12 +8814,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -8829,26 +8829,26 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>(0, 1, 1, 12)</t>
+          <t>(2, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F183" t="n">
-        <v>5658.85</v>
+        <v>7765.95</v>
       </c>
       <c r="G183" t="n">
-        <v>5439.82</v>
+        <v>7543.24</v>
       </c>
       <c r="H183" t="n">
-        <v>11.46</v>
+        <v>15.55</v>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>[38529.75, 42745.65, 52335.45]</t>
+          <t>[46813.33, 38742.16, 38910.09]</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>[45002.3, 49356.3, 49099.2]</t>
+          <t>[51783.9, 47959.4, 47352.0]</t>
         </is>
       </c>
     </row>
@@ -8860,12 +8860,12 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -8879,22 +8879,22 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>14550.39</v>
+        <v>2981.17</v>
       </c>
       <c r="G184" t="n">
-        <v>12476.64</v>
+        <v>2918.36</v>
       </c>
       <c r="H184" t="n">
-        <v>24.78</v>
+        <v>6.09</v>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>[51531.56, 64609.48, 71244.69]</t>
+          <t>[44187.6, 44762.55, 46047.66]</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>[49356.3, 49099.2, 51500.3]</t>
+          <t>[47959.4, 47352.0, 48441.5]</t>
         </is>
       </c>
     </row>
@@ -8906,17 +8906,17 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>(2, 0, 1)</t>
+          <t>(3, 0, 0)</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -8925,22 +8925,22 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>16030.54</v>
+        <v>2358.04</v>
       </c>
       <c r="G185" t="n">
-        <v>15555.03</v>
+        <v>2331.34</v>
       </c>
       <c r="H185" t="n">
-        <v>29.44</v>
+        <v>4.88</v>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>[60348.73, 66271.06, 76878.48]</t>
+          <t>[49473.16, 51271.21, 49370.16]</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>[49099.2, 51500.3, 56233.7]</t>
+          <t>[47352.0, 48441.5, 47327.0]</t>
         </is>
       </c>
     </row>
@@ -8952,12 +8952,12 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -8971,22 +8971,22 @@
         </is>
       </c>
       <c r="F186" t="n">
-        <v>2641.31</v>
+        <v>520.3</v>
       </c>
       <c r="G186" t="n">
-        <v>1998.38</v>
+        <v>392.78</v>
       </c>
       <c r="H186" t="n">
-        <v>3.5</v>
+        <v>0.84</v>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>[50791.55, 57080.47, 62700.71]</t>
+          <t>[48475.77, 46475.22, 43973.11]</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>[51500.3, 56233.7, 58261.1]</t>
+          <t>[48441.5, 47327.0, 44265.4]</t>
         </is>
       </c>
     </row>
@@ -8998,12 +8998,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -9017,22 +9017,22 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>3786.43</v>
+        <v>920.25</v>
       </c>
       <c r="G187" t="n">
-        <v>3412.02</v>
+        <v>838.6</v>
       </c>
       <c r="H187" t="n">
-        <v>6.02</v>
+        <v>1.76</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>[58120.7, 63951.7, 56420.97]</t>
+          <t>[46431.1, 43916.93, 47801.58]</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>[56233.7, 58261.1, 53762.5]</t>
+          <t>[47327.0, 44265.4, 49073.0]</t>
         </is>
       </c>
     </row>
@@ -9044,12 +9044,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -9059,26 +9059,26 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>(2, 1, 1, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F188" t="n">
-        <v>3380.17</v>
+        <v>1502.91</v>
       </c>
       <c r="G188" t="n">
-        <v>2561.63</v>
+        <v>1081.29</v>
       </c>
       <c r="H188" t="n">
-        <v>4.8</v>
+        <v>2.14</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>[60213.03, 53544.91, 46268.54]</t>
+          <t>[44981.71, 49047.92, 55311.29]</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>[58261.1, 53762.5, 51783.9]</t>
+          <t>[44265.4, 49073.0, 52808.8]</t>
         </is>
       </c>
     </row>
@@ -9090,12 +9090,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -9109,22 +9109,22 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>8658.629999999999</v>
+        <v>1095.01</v>
       </c>
       <c r="G189" t="n">
-        <v>7848.34</v>
+        <v>1068.16</v>
       </c>
       <c r="H189" t="n">
-        <v>15.7</v>
+        <v>2.03</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>[50600.76, 43486.99, 35873.05]</t>
+          <t>[48064.61, 54197.42, 58068.56]</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>[53762.5, 51783.9, 47959.4]</t>
+          <t>[49073.0, 52808.8, 57261.1]</t>
         </is>
       </c>
     </row>
@@ -9136,12 +9136,12 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -9151,26 +9151,26 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>(2, 1, 1, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F190" t="n">
-        <v>7765.95</v>
+        <v>5148.35</v>
       </c>
       <c r="G190" t="n">
-        <v>7543.24</v>
+        <v>4476.77</v>
       </c>
       <c r="H190" t="n">
-        <v>15.55</v>
+        <v>7.8</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>[46813.33, 38742.16, 38910.09]</t>
+          <t>[55664.88, 59768.64, 67348.2]</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>[51783.9, 47959.4, 47352.0]</t>
+          <t>[52808.8, 57261.1, 59281.5]</t>
         </is>
       </c>
     </row>
@@ -9182,12 +9182,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -9201,22 +9201,22 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>2981.17</v>
+        <v>3076.21</v>
       </c>
       <c r="G191" t="n">
-        <v>2918.36</v>
+        <v>2867.59</v>
       </c>
       <c r="H191" t="n">
-        <v>6.09</v>
+        <v>4.73</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>[44187.6, 44762.55, 46047.66]</t>
+          <t>[55903.08, 62515.39, 67019.45]</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>[47959.4, 47352.0, 48441.5]</t>
+          <t>[57261.1, 59281.5, 63008.6]</t>
         </is>
       </c>
     </row>
@@ -9228,41 +9228,41 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>(0, 0, 2)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 0, 12)</t>
         </is>
       </c>
       <c r="F192" t="n">
-        <v>5071.67</v>
+        <v>2489.35</v>
       </c>
       <c r="G192" t="n">
-        <v>4559.64</v>
+        <v>2124.99</v>
       </c>
       <c r="H192" t="n">
-        <v>30.71</v>
+        <v>9.17</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>[18980.91, 20136.11, 25107.61]</t>
+          <t>[26434.14, 26249.11, 21986.71]</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>[16642.4, 12543.1, 21360.2]</t>
+          <t>[23808.0, 22847.1, 21639.9]</t>
         </is>
       </c>
     </row>
@@ -9274,41 +9274,41 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2024-02</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>(0, 0, 2)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>(1, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F193" t="n">
-        <v>2938.15</v>
+        <v>663.37</v>
       </c>
       <c r="G193" t="n">
-        <v>2528.32</v>
+        <v>559.3200000000001</v>
       </c>
       <c r="H193" t="n">
-        <v>16.64</v>
+        <v>2.73</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>[17108.98, 23366.43, 25482.56]</t>
+          <t>[22614.81, 21249.63, 18603.99]</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>[12543.1, 21360.2, 24469.7]</t>
+          <t>[22847.1, 21639.9, 19659.4]</t>
         </is>
       </c>
     </row>
@@ -9320,17 +9320,17 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>(0, 0, 2)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -9339,22 +9339,22 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>4039.2</v>
+        <v>826.4400000000001</v>
       </c>
       <c r="G194" t="n">
-        <v>3757.68</v>
+        <v>738.6799999999999</v>
       </c>
       <c r="H194" t="n">
-        <v>16.6</v>
+        <v>3.73</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>[15567.41, 21298.07, 26062.84]</t>
+          <t>[21424.43, 18632.04, 20550.01]</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>[21360.2, 24469.7, 23754.2]</t>
+          <t>[21639.9, 19659.4, 19576.8]</t>
         </is>
       </c>
     </row>
@@ -9366,17 +9366,17 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>(0, 0, 1)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -9385,22 +9385,22 @@
         </is>
       </c>
       <c r="F195" t="n">
-        <v>3160.73</v>
+        <v>852.04</v>
       </c>
       <c r="G195" t="n">
-        <v>3060.64</v>
+        <v>841.75</v>
       </c>
       <c r="H195" t="n">
-        <v>12.91</v>
+        <v>4.34</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>[28539.27, 26723.42, 24492.83]</t>
+          <t>[18823.69, 20583.15, 18147.3]</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>[24469.7, 23754.2, 22349.7]</t>
+          <t>[19659.4, 19576.8, 18830.5]</t>
         </is>
       </c>
     </row>
@@ -9412,12 +9412,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -9427,26 +9427,26 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F196" t="n">
-        <v>1004.29</v>
+        <v>1061.01</v>
       </c>
       <c r="G196" t="n">
-        <v>769.87</v>
+        <v>793.99</v>
       </c>
       <c r="H196" t="n">
-        <v>3.43</v>
+        <v>4.13</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>[23767.26, 21642.19, 20848.36]</t>
+          <t>[21347.41, 18358.58, 16406.16]</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>[23754.2, 22349.7, 22437.4]</t>
+          <t>[19576.8, 18830.5, 16545.6]</t>
         </is>
       </c>
     </row>
@@ -9458,17 +9458,17 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>(0, 0, 1)</t>
+          <t>(1, 0, 1)</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -9477,22 +9477,22 @@
         </is>
       </c>
       <c r="F197" t="n">
-        <v>1026.06</v>
+        <v>1934.51</v>
       </c>
       <c r="G197" t="n">
-        <v>833.41</v>
+        <v>1552.63</v>
       </c>
       <c r="H197" t="n">
-        <v>3.64</v>
+        <v>7.68</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>[23849.25, 22485.5, 24760.58]</t>
+          <t>[17097.09, 16487.99, 24139.27]</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>[22349.7, 22437.4, 23808.0]</t>
+          <t>[18830.5, 16545.6, 21272.4]</t>
         </is>
       </c>
     </row>
@@ -9504,12 +9504,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -9519,26 +9519,26 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>2070.28</v>
+        <v>2765.48</v>
       </c>
       <c r="G198" t="n">
-        <v>1882.53</v>
+        <v>2636.23</v>
       </c>
       <c r="H198" t="n">
-        <v>8.18</v>
+        <v>12.62</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>[21410.26, 25366.95, 25908.61]</t>
+          <t>[18082.67, 24833.94, 26567.17]</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>[22437.4, 23808.0, 22847.1]</t>
+          <t>[16545.6, 21272.4, 23757.1]</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -9565,26 +9565,26 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>(0, 1, 0, 12)</t>
+          <t>(0, 1, 1, 12)</t>
         </is>
       </c>
       <c r="F199" t="n">
-        <v>2489.35</v>
+        <v>1959.52</v>
       </c>
       <c r="G199" t="n">
-        <v>2124.99</v>
+        <v>1886.54</v>
       </c>
       <c r="H199" t="n">
-        <v>9.17</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>[26434.14, 26249.11, 21986.71]</t>
+          <t>[23497.9, 26052.84, 26457.49]</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>[23808.0, 22847.1, 21639.9]</t>
+          <t>[21272.4, 23757.1, 25319.1]</t>
         </is>
       </c>
     </row>
@@ -9596,12 +9596,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -9615,22 +9615,22 @@
         </is>
       </c>
       <c r="F200" t="n">
-        <v>663.37</v>
+        <v>1685.97</v>
       </c>
       <c r="G200" t="n">
-        <v>559.3200000000001</v>
+        <v>1333.14</v>
       </c>
       <c r="H200" t="n">
-        <v>2.73</v>
+        <v>5.03</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>[22614.81, 21249.63, 18603.99]</t>
+          <t>[24156.59, 26147.42, 24580.7]</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>[22847.1, 21639.9, 19659.4]</t>
+          <t>[23757.1, 25319.1, 27352.3]</t>
         </is>
       </c>
     </row>
@@ -9642,12 +9642,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -9661,22 +9661,22 @@
         </is>
       </c>
       <c r="F201" t="n">
-        <v>826.4400000000001</v>
+        <v>1710.44</v>
       </c>
       <c r="G201" t="n">
-        <v>738.6799999999999</v>
+        <v>1213.66</v>
       </c>
       <c r="H201" t="n">
-        <v>3.73</v>
+        <v>4.54</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>[21424.43, 18632.04, 20550.01]</t>
+          <t>[25750.2, 24436.0, 23754.29]</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>[21639.9, 19659.4, 19576.8]</t>
+          <t>[25319.1, 27352.3, 23460.7]</t>
         </is>
       </c>
     </row>
